--- a/Results/3_analysis/iML1515_alternative_models_predictions_csources.xlsx
+++ b/Results/3_analysis/iML1515_alternative_models_predictions_csources.xlsx
@@ -6820,7 +6820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M742"/>
+  <dimension ref="A1:O742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6889,6 +6889,16 @@
           <t>ME2</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>EX_co2_e</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>EX_o2_e</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6932,6 +6942,12 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
+      <c r="N2" t="n">
+        <v>20.01101770001771</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-20.12842001957925</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6975,6 +6991,12 @@
       <c r="M3" t="n">
         <v>0</v>
       </c>
+      <c r="N3" t="n">
+        <v>4.890847570250746</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-4.911226424132211</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7018,6 +7040,12 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
+      <c r="N4" t="n">
+        <v>7.483532281424769</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-7.520547935946336</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7061,6 +7089,12 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
+      <c r="N5" t="n">
+        <v>10.74159625475847</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-10.7995183313234</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7104,6 +7138,12 @@
       <c r="M6" t="n">
         <v>0</v>
       </c>
+      <c r="N6" t="n">
+        <v>14.02260434058045</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-14.10158006751298</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7147,6 +7187,12 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
+      <c r="N7" t="n">
+        <v>8.004225428519954</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-8.044582279156</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7190,6 +7236,12 @@
       <c r="M8" t="n">
         <v>0</v>
       </c>
+      <c r="N8" t="n">
+        <v>8.698729892900939</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-8.743543256227362</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7233,6 +7285,12 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
+      <c r="N9" t="n">
+        <v>9.363038511004426</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-9.412114625599976</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7276,6 +7334,12 @@
       <c r="M10" t="n">
         <v>0</v>
       </c>
+      <c r="N10" t="n">
+        <v>10.37570408738174</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-10.43127829842408</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7319,6 +7383,12 @@
       <c r="M11" t="n">
         <v>0</v>
       </c>
+      <c r="N11" t="n">
+        <v>12.63425519105965</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-12.70432212629846</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7362,6 +7432,12 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
+      <c r="N12" t="n">
+        <v>13.18544921040962</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-13.25905306048208</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7405,6 +7481,12 @@
       <c r="M13" t="n">
         <v>0</v>
       </c>
+      <c r="N13" t="n">
+        <v>16.16061506834279</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-16.25331003313372</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7448,6 +7530,12 @@
       <c r="M14" t="n">
         <v>0</v>
       </c>
+      <c r="N14" t="n">
+        <v>16.89727039925167</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-16.99469235141132</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7491,6 +7579,12 @@
       <c r="M15" t="n">
         <v>0</v>
       </c>
+      <c r="N15" t="n">
+        <v>3.135533917722148</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-3.14453096431851</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7534,6 +7628,12 @@
       <c r="M16" t="n">
         <v>0</v>
       </c>
+      <c r="N16" t="n">
+        <v>3.818355059775416</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-3.831790817253806</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7577,6 +7677,12 @@
       <c r="M17" t="n">
         <v>0</v>
       </c>
+      <c r="N17" t="n">
+        <v>3.59074801242433</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-3.602704199608708</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7620,6 +7726,12 @@
       <c r="M18" t="n">
         <v>0</v>
       </c>
+      <c r="N18" t="n">
+        <v>4.959679907715566</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-4.980500446569756</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7663,6 +7775,12 @@
       <c r="M19" t="n">
         <v>0</v>
       </c>
+      <c r="N19" t="n">
+        <v>5.189121032598216</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-5.211413854694896</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7706,6 +7824,12 @@
       <c r="M20" t="n">
         <v>0</v>
       </c>
+      <c r="N20" t="n">
+        <v>5.648003282363518</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-5.673240670945181</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7749,6 +7873,12 @@
       <c r="M21" t="n">
         <v>0</v>
       </c>
+      <c r="N21" t="n">
+        <v>10.69570802978193</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-10.75333564969838</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7792,6 +7922,12 @@
       <c r="M22" t="n">
         <v>0</v>
       </c>
+      <c r="N22" t="n">
+        <v>11.61347252931259</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-11.67698928219894</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7835,6 +7971,12 @@
       <c r="M23" t="n">
         <v>0</v>
       </c>
+      <c r="N23" t="n">
+        <v>14.13732490302181</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-14.21703677157555</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7878,6 +8020,12 @@
       <c r="M24" t="n">
         <v>0</v>
       </c>
+      <c r="N24" t="n">
+        <v>14.36676602790446</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-14.44795017970068</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7921,6 +8069,12 @@
       <c r="M25" t="n">
         <v>0</v>
       </c>
+      <c r="N25" t="n">
+        <v>4.546697611298897</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-4.564867993718133</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7964,6 +8118,12 @@
       <c r="M26" t="n">
         <v>0</v>
       </c>
+      <c r="N26" t="n">
+        <v>6.726376569312006</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-6.758533689133375</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8007,6 +8167,12 @@
       <c r="M27" t="n">
         <v>0</v>
       </c>
+      <c r="N27" t="n">
+        <v>10.81042859222327</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-10.86879235376094</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8050,6 +8216,12 @@
       <c r="M28" t="n">
         <v>0</v>
       </c>
+      <c r="N28" t="n">
+        <v>22.92491998602742</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-23.0610203027686</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8093,6 +8265,12 @@
       <c r="M29" t="n">
         <v>0</v>
       </c>
+      <c r="N29" t="n">
+        <v>2.679650149181639</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-2.685683855824411</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8136,6 +8314,12 @@
       <c r="M30" t="n">
         <v>0</v>
       </c>
+      <c r="N30" t="n">
+        <v>3.828974347499023</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-3.842479136155672</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8179,6 +8363,12 @@
       <c r="M31" t="n">
         <v>0</v>
       </c>
+      <c r="N31" t="n">
+        <v>6.001953240837818</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-6.029461863893308</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8222,6 +8412,12 @@
       <c r="M32" t="n">
         <v>0</v>
       </c>
+      <c r="N32" t="n">
+        <v>8.734317854585026</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-8.779359579586609</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8265,6 +8461,12 @@
       <c r="M33" t="n">
         <v>0</v>
       </c>
+      <c r="N33" t="n">
+        <v>11.82651630313832</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-11.89140012035674</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8308,6 +8510,12 @@
       <c r="M34" t="n">
         <v>0</v>
       </c>
+      <c r="N34" t="n">
+        <v>14.70123276362203</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-14.78456312948705</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8351,6 +8559,12 @@
       <c r="M35" t="n">
         <v>0</v>
       </c>
+      <c r="N35" t="n">
+        <v>19.12600266634725</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-19.23772600048677</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8394,6 +8608,12 @@
       <c r="M36" t="n">
         <v>0</v>
       </c>
+      <c r="N36" t="n">
+        <v>26.98602789645039</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-27.14818762658365</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8437,6 +8657,12 @@
       <c r="M37" t="n">
         <v>0</v>
       </c>
+      <c r="N37" t="n">
+        <v>6.336326657011491</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-6.365980895320624</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8480,6 +8706,12 @@
       <c r="M38" t="n">
         <v>0</v>
       </c>
+      <c r="N38" t="n">
+        <v>20.76817341213042</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-20.89043426639221</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8523,6 +8755,12 @@
       <c r="M39" t="n">
         <v>0</v>
       </c>
+      <c r="N39" t="n">
+        <v>18.9785326380458</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-19.08930968301609</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8566,6 +8804,12 @@
       <c r="M40" t="n">
         <v>0</v>
       </c>
+      <c r="N40" t="n">
+        <v>18.35904160086264</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-18.4658434810782</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8609,6 +8853,12 @@
       <c r="M41" t="n">
         <v>0</v>
       </c>
+      <c r="N41" t="n">
+        <v>8.432243797941149</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-8.219026794914557</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8652,6 +8902,12 @@
       <c r="M42" t="n">
         <v>0</v>
       </c>
+      <c r="N42" t="n">
+        <v>3.543114415788772</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-3.437136598548186</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8695,6 +8951,12 @@
       <c r="M43" t="n">
         <v>0</v>
       </c>
+      <c r="N43" t="n">
+        <v>4.955129536760089</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-4.814585063563517</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8738,6 +9000,12 @@
       <c r="M44" t="n">
         <v>0</v>
       </c>
+      <c r="N44" t="n">
+        <v>7.412306500988291</v>
+      </c>
+      <c r="O44" t="n">
+        <v>-7.242563583295334</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8781,6 +9049,12 @@
       <c r="M45" t="n">
         <v>0</v>
       </c>
+      <c r="N45" t="n">
+        <v>7.773323910553289</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-7.588192888398185</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8824,6 +9098,12 @@
       <c r="M46" t="n">
         <v>0</v>
       </c>
+      <c r="N46" t="n">
+        <v>5.386423447762691</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-5.24095661605352</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8867,6 +9147,12 @@
       <c r="M47" t="n">
         <v>0</v>
       </c>
+      <c r="N47" t="n">
+        <v>5.961686533752267</v>
+      </c>
+      <c r="O47" t="n">
+        <v>-5.809654222967096</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8910,6 +9196,12 @@
       <c r="M48" t="n">
         <v>0</v>
       </c>
+      <c r="N48" t="n">
+        <v>6.511938181220562</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-6.353625846971378</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8953,6 +9245,12 @@
       <c r="M49" t="n">
         <v>0</v>
       </c>
+      <c r="N49" t="n">
+        <v>7.350736424312486</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-7.18285088356328</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8996,6 +9294,12 @@
       <c r="M50" t="n">
         <v>0</v>
       </c>
+      <c r="N50" t="n">
+        <v>7.617321121141019</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-7.438839604401064</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9039,6 +9343,12 @@
       <c r="M51" t="n">
         <v>0</v>
       </c>
+      <c r="N51" t="n">
+        <v>7.677970321042177</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-7.496903676275418</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9082,6 +9392,12 @@
       <c r="M52" t="n">
         <v>0</v>
       </c>
+      <c r="N52" t="n">
+        <v>8.005334955857078</v>
+      </c>
+      <c r="O52" t="n">
+        <v>-7.810314631671329</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9125,6 +9441,12 @@
       <c r="M53" t="n">
         <v>0</v>
       </c>
+      <c r="N53" t="n">
+        <v>8.086390908668726</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-7.887915633458173</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9168,6 +9490,12 @@
       <c r="M54" t="n">
         <v>0</v>
       </c>
+      <c r="N54" t="n">
+        <v>3.841351750304128</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-3.770372320774944</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9211,6 +9539,12 @@
       <c r="M55" t="n">
         <v>0</v>
       </c>
+      <c r="N55" t="n">
+        <v>3.708736757586559</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-3.623219382451798</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9254,6 +9588,12 @@
       <c r="M56" t="n">
         <v>0</v>
       </c>
+      <c r="N56" t="n">
+        <v>3.752941755159042</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-3.672270361892813</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9297,6 +9637,12 @@
       <c r="M57" t="n">
         <v>0</v>
       </c>
+      <c r="N57" t="n">
+        <v>3.531163476590318</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-3.424041179337001</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9340,6 +9686,12 @@
       <c r="M58" t="n">
         <v>0</v>
       </c>
+      <c r="N58" t="n">
+        <v>3.499277980396592</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-3.388051438675393</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9383,6 +9735,12 @@
       <c r="M59" t="n">
         <v>0</v>
       </c>
+      <c r="N59" t="n">
+        <v>3.45777102534313</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-3.339596461707212</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9426,6 +9784,12 @@
       <c r="M60" t="n">
         <v>0</v>
       </c>
+      <c r="N60" t="n">
+        <v>7.404028183768816</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-7.234638123325294</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9469,6 +9833,12 @@
       <c r="M61" t="n">
         <v>0</v>
       </c>
+      <c r="N61" t="n">
+        <v>7.505012268300789</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-7.331317834714572</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9512,6 +9882,12 @@
       <c r="M62" t="n">
         <v>0</v>
       </c>
+      <c r="N62" t="n">
+        <v>7.782718500764399</v>
+      </c>
+      <c r="O62" t="n">
+        <v>-7.597187041035578</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9555,6 +9931,12 @@
       <c r="M63" t="n">
         <v>0</v>
       </c>
+      <c r="N63" t="n">
+        <v>7.807964521897429</v>
+      </c>
+      <c r="O63" t="n">
+        <v>-7.621356968882929</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9598,6 +9980,12 @@
       <c r="M64" t="n">
         <v>0</v>
       </c>
+      <c r="N64" t="n">
+        <v>3.588565334798383</v>
+      </c>
+      <c r="O64" t="n">
+        <v>-3.488830558128334</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9641,6 +10029,12 @@
       <c r="M65" t="n">
         <v>0</v>
       </c>
+      <c r="N65" t="n">
+        <v>4.337343956084666</v>
+      </c>
+      <c r="O65" t="n">
+        <v>-4.205999785372814</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9684,6 +10078,12 @@
       <c r="M66" t="n">
         <v>0</v>
       </c>
+      <c r="N66" t="n">
+        <v>7.416640790146953</v>
+      </c>
+      <c r="O66" t="n">
+        <v>-7.24671312653157</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9727,6 +10127,12 @@
       <c r="M67" t="n">
         <v>0</v>
       </c>
+      <c r="N67" t="n">
+        <v>8.749627227192503</v>
+      </c>
+      <c r="O67" t="n">
+        <v>-8.52288198637328</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9770,6 +10176,12 @@
       <c r="M68" t="n">
         <v>0</v>
       </c>
+      <c r="N68" t="n">
+        <v>3.179319770909455</v>
+      </c>
+      <c r="O68" t="n">
+        <v>-3.1263447632823</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9813,6 +10225,12 @@
       <c r="M69" t="n">
         <v>0</v>
       </c>
+      <c r="N69" t="n">
+        <v>3.706678285480447</v>
+      </c>
+      <c r="O69" t="n">
+        <v>-3.620934680936481</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9856,6 +10274,12 @@
       <c r="M70" t="n">
         <v>0</v>
       </c>
+      <c r="N70" t="n">
+        <v>3.746469213851976</v>
+      </c>
+      <c r="O70" t="n">
+        <v>-3.62397196672678</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9899,6 +10323,12 @@
       <c r="M71" t="n">
         <v>0</v>
       </c>
+      <c r="N71" t="n">
+        <v>5.991683625499693</v>
+      </c>
+      <c r="O71" t="n">
+        <v>-5.839428067689894</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9942,6 +10372,12 @@
       <c r="M72" t="n">
         <v>0</v>
       </c>
+      <c r="N72" t="n">
+        <v>7.52844334903858</v>
+      </c>
+      <c r="O72" t="n">
+        <v>-7.353750182680744</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9985,6 +10421,12 @@
       <c r="M73" t="n">
         <v>0</v>
       </c>
+      <c r="N73" t="n">
+        <v>7.844755270654772</v>
+      </c>
+      <c r="O73" t="n">
+        <v>-7.656579538737772</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10028,6 +10470,12 @@
       <c r="M74" t="n">
         <v>0</v>
       </c>
+      <c r="N74" t="n">
+        <v>8.331623276553614</v>
+      </c>
+      <c r="O74" t="n">
+        <v>-8.122695150055202</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10071,6 +10519,12 @@
       <c r="M75" t="n">
         <v>0</v>
       </c>
+      <c r="N75" t="n">
+        <v>9.098642840302196</v>
+      </c>
+      <c r="O75" t="n">
+        <v>-9.48539095336896</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10114,6 +10568,12 @@
       <c r="M76" t="n">
         <v>0</v>
       </c>
+      <c r="N76" t="n">
+        <v>4.019199856201765</v>
+      </c>
+      <c r="O76" t="n">
+        <v>-3.892619007960541</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10157,6 +10617,12 @@
       <c r="M77" t="n">
         <v>0</v>
       </c>
+      <c r="N77" t="n">
+        <v>8.512328511491413</v>
+      </c>
+      <c r="O77" t="n">
+        <v>-8.295697955807031</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10200,6 +10666,12 @@
       <c r="M78" t="n">
         <v>0</v>
       </c>
+      <c r="N78" t="n">
+        <v>8.315409546654456</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-8.107172518598382</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10243,6 +10715,12 @@
       <c r="M79" t="n">
         <v>0</v>
       </c>
+      <c r="N79" t="n">
+        <v>8.247245289595483</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-8.041913713410757</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10286,6 +10764,12 @@
       <c r="M80" t="n">
         <v>0</v>
       </c>
+      <c r="N80" t="n">
+        <v>25.46257099290461</v>
+      </c>
+      <c r="O80" t="n">
+        <v>-24.20970465511189</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10329,6 +10813,12 @@
       <c r="M81" t="n">
         <v>0</v>
       </c>
+      <c r="N81" t="n">
+        <v>4.890847570250742</v>
+      </c>
+      <c r="O81" t="n">
+        <v>-4.624174207762639</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10372,6 +10862,12 @@
       <c r="M82" t="n">
         <v>0</v>
       </c>
+      <c r="N82" t="n">
+        <v>7.483532281424746</v>
+      </c>
+      <c r="O82" t="n">
+        <v>-6.99915327201679</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10415,6 +10911,12 @@
       <c r="M83" t="n">
         <v>0</v>
       </c>
+      <c r="N83" t="n">
+        <v>10.78727706422033</v>
+      </c>
+      <c r="O83" t="n">
+        <v>-10.03169607019209</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10458,6 +10960,12 @@
       <c r="M84" t="n">
         <v>0</v>
       </c>
+      <c r="N84" t="n">
+        <v>15.57525961162933</v>
+      </c>
+      <c r="O84" t="n">
+        <v>-14.62252517781823</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10501,6 +11009,12 @@
       <c r="M85" t="n">
         <v>0</v>
       </c>
+      <c r="N85" t="n">
+        <v>8.004225428519943</v>
+      </c>
+      <c r="O85" t="n">
+        <v>-7.476124234942612</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10544,6 +11058,12 @@
       <c r="M86" t="n">
         <v>0</v>
       </c>
+      <c r="N86" t="n">
+        <v>8.698729892900918</v>
+      </c>
+      <c r="O86" t="n">
+        <v>-8.11231171883801</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10587,6 +11107,12 @@
       <c r="M87" t="n">
         <v>0</v>
       </c>
+      <c r="N87" t="n">
+        <v>9.363038511004477</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-8.720838877346642</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10630,6 +11156,12 @@
       <c r="M88" t="n">
         <v>0</v>
       </c>
+      <c r="N88" t="n">
+        <v>10.37570408738179</v>
+      </c>
+      <c r="O88" t="n">
+        <v>-9.648471740926858</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10673,6 +11205,12 @@
       <c r="M89" t="n">
         <v>0</v>
       </c>
+      <c r="N89" t="n">
+        <v>13.34889800624031</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-12.4691724387426</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10716,6 +11254,12 @@
       <c r="M90" t="n">
         <v>0</v>
       </c>
+      <c r="N90" t="n">
+        <v>14.19562613922082</v>
+      </c>
+      <c r="O90" t="n">
+        <v>-13.2849825753202</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10759,6 +11303,12 @@
       <c r="M91" t="n">
         <v>0</v>
       </c>
+      <c r="N91" t="n">
+        <v>19.09870593368407</v>
+      </c>
+      <c r="O91" t="n">
+        <v>-18.03847561510029</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10802,6 +11352,12 @@
       <c r="M92" t="n">
         <v>0</v>
       </c>
+      <c r="N92" t="n">
+        <v>20.31294033948659</v>
+      </c>
+      <c r="O92" t="n">
+        <v>-19.21568381484829</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10845,6 +11401,12 @@
       <c r="M93" t="n">
         <v>0</v>
       </c>
+      <c r="N93" t="n">
+        <v>3.135533906065509</v>
+      </c>
+      <c r="O93" t="n">
+        <v>-3.017800460670641</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10888,6 +11450,12 @@
       <c r="M94" t="n">
         <v>0</v>
       </c>
+      <c r="N94" t="n">
+        <v>3.818355042367931</v>
+      </c>
+      <c r="O94" t="n">
+        <v>-3.642537566879737</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10931,6 +11499,12 @@
       <c r="M95" t="n">
         <v>0</v>
       </c>
+      <c r="N95" t="n">
+        <v>3.590747996933787</v>
+      </c>
+      <c r="O95" t="n">
+        <v>-3.434291864810038</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10974,6 +11548,12 @@
       <c r="M96" t="n">
         <v>0</v>
       </c>
+      <c r="N96" t="n">
+        <v>4.95967987048106</v>
+      </c>
+      <c r="O96" t="n">
+        <v>-4.68722671012113</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11017,6 +11597,12 @@
       <c r="M97" t="n">
         <v>0</v>
       </c>
+      <c r="N97" t="n">
+        <v>5.189120992730714</v>
+      </c>
+      <c r="O97" t="n">
+        <v>-4.897401845780828</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11060,6 +11646,12 @@
       <c r="M98" t="n">
         <v>0</v>
       </c>
+      <c r="N98" t="n">
+        <v>5.648003237230092</v>
+      </c>
+      <c r="O98" t="n">
+        <v>-5.317752117100254</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11103,6 +11695,12 @@
       <c r="M99" t="n">
         <v>0</v>
       </c>
+      <c r="N99" t="n">
+        <v>10.72986099458145</v>
+      </c>
+      <c r="O99" t="n">
+        <v>-9.977533845584302</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11146,6 +11744,12 @@
       <c r="M100" t="n">
         <v>0</v>
       </c>
+      <c r="N100" t="n">
+        <v>11.8856392446431</v>
+      </c>
+      <c r="O100" t="n">
+        <v>-11.06862288972323</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11189,6 +11793,12 @@
       <c r="M101" t="n">
         <v>0</v>
       </c>
+      <c r="N101" t="n">
+        <v>15.76431934764898</v>
+      </c>
+      <c r="O101" t="n">
+        <v>-14.80581694073969</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11232,6 +11842,12 @@
       <c r="M102" t="n">
         <v>0</v>
       </c>
+      <c r="N102" t="n">
+        <v>16.14243881968828</v>
+      </c>
+      <c r="O102" t="n">
+        <v>-15.17240046658275</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11275,6 +11891,12 @@
       <c r="M103" t="n">
         <v>0</v>
       </c>
+      <c r="N103" t="n">
+        <v>4.546697587757198</v>
+      </c>
+      <c r="O103" t="n">
+        <v>-4.308923813502775</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11318,6 +11940,12 @@
       <c r="M104" t="n">
         <v>0</v>
       </c>
+      <c r="N104" t="n">
+        <v>6.726376511803651</v>
+      </c>
+      <c r="O104" t="n">
+        <v>-6.305575254700915</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11361,6 +11989,12 @@
       <c r="M105" t="n">
         <v>0</v>
       </c>
+      <c r="N105" t="n">
+        <v>10.87340147791321</v>
+      </c>
+      <c r="O105" t="n">
+        <v>-10.112939732416</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11404,6 +12038,12 @@
       <c r="M106" t="n">
         <v>0</v>
       </c>
+      <c r="N106" t="n">
+        <v>26.28630082998833</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-24.93705914815405</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11447,6 +12087,12 @@
       <c r="M107" t="n">
         <v>0</v>
       </c>
+      <c r="N107" t="n">
+        <v>2.67965013892166</v>
+      </c>
+      <c r="O107" t="n">
+        <v>-2.600696490699565</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11490,6 +12136,12 @@
       <c r="M108" t="n">
         <v>0</v>
       </c>
+      <c r="N108" t="n">
+        <v>3.828974330002104</v>
+      </c>
+      <c r="O108" t="n">
+        <v>-3.652253527142033</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11533,6 +12185,12 @@
       <c r="M109" t="n">
         <v>0</v>
       </c>
+      <c r="N109" t="n">
+        <v>6.001953191642621</v>
+      </c>
+      <c r="O109" t="n">
+        <v>-5.641981178377452</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11576,6 +12234,12 @@
       <c r="M110" t="n">
         <v>0</v>
       </c>
+      <c r="N110" t="n">
+        <v>8.734317854585058</v>
+      </c>
+      <c r="O110" t="n">
+        <v>-8.14491138804383</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11619,6 +12283,12 @@
       <c r="M111" t="n">
         <v>0</v>
       </c>
+      <c r="N111" t="n">
+        <v>12.1628750581325</v>
+      </c>
+      <c r="O111" t="n">
+        <v>-11.33130704249058</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11662,6 +12332,12 @@
       <c r="M112" t="n">
         <v>0</v>
       </c>
+      <c r="N112" t="n">
+        <v>16.69364072657816</v>
+      </c>
+      <c r="O112" t="n">
+        <v>-15.70678590141215</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11705,6 +12381,12 @@
       <c r="M113" t="n">
         <v>0</v>
       </c>
+      <c r="N113" t="n">
+        <v>23.98934312410134</v>
+      </c>
+      <c r="O113" t="n">
+        <v>-22.78020859966069</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11748,6 +12430,12 @@
       <c r="M114" t="n">
         <v>0</v>
       </c>
+      <c r="N114" t="n">
+        <v>27.17828924329993</v>
+      </c>
+      <c r="O114" t="n">
+        <v>-25.70329902033588</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11791,6 +12479,12 @@
       <c r="M115" t="n">
         <v>0</v>
       </c>
+      <c r="N115" t="n">
+        <v>6.336326603979203</v>
+      </c>
+      <c r="O115" t="n">
+        <v>-5.948277524079399</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11834,6 +12528,12 @@
       <c r="M116" t="n">
         <v>0</v>
       </c>
+      <c r="N116" t="n">
+        <v>25.81258946878433</v>
+      </c>
+      <c r="O116" t="n">
+        <v>-24.53012949807534</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11877,6 +12577,12 @@
       <c r="M117" t="n">
         <v>0</v>
       </c>
+      <c r="N117" t="n">
+        <v>23.74608410625511</v>
+      </c>
+      <c r="O117" t="n">
+        <v>-22.54435228875218</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11920,6 +12626,12 @@
       <c r="M118" t="n">
         <v>0</v>
       </c>
+      <c r="N118" t="n">
+        <v>22.72420336818408</v>
+      </c>
+      <c r="O118" t="n">
+        <v>-21.55356878885686</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11963,6 +12675,12 @@
       <c r="M119" t="n">
         <v>0</v>
       </c>
+      <c r="N119" t="n">
+        <v>23.75849617709124</v>
+      </c>
+      <c r="O119" t="n">
+        <v>-22.41703209000401</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12006,6 +12724,12 @@
       <c r="M120" t="n">
         <v>0</v>
       </c>
+      <c r="N120" t="n">
+        <v>4.890847533806132</v>
+      </c>
+      <c r="O120" t="n">
+        <v>-4.624174169423202</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12049,6 +12773,12 @@
       <c r="M121" t="n">
         <v>0</v>
       </c>
+      <c r="N121" t="n">
+        <v>7.483532281424745</v>
+      </c>
+      <c r="O121" t="n">
+        <v>-6.999153272016788</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12092,6 +12822,12 @@
       <c r="M122" t="n">
         <v>0</v>
       </c>
+      <c r="N122" t="n">
+        <v>10.74159625475843</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-9.98364023771669</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12135,6 +12871,12 @@
       <c r="M123" t="n">
         <v>0</v>
       </c>
+      <c r="N123" t="n">
+        <v>14.36745101459959</v>
+      </c>
+      <c r="O123" t="n">
+        <v>-13.35192055664533</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12178,6 +12920,12 @@
       <c r="M124" t="n">
         <v>0</v>
       </c>
+      <c r="N124" t="n">
+        <v>8.004225428519957</v>
+      </c>
+      <c r="O124" t="n">
+        <v>-7.476124234942622</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12221,6 +12969,12 @@
       <c r="M125" t="n">
         <v>0</v>
       </c>
+      <c r="N125" t="n">
+        <v>8.69872989290092</v>
+      </c>
+      <c r="O125" t="n">
+        <v>-8.112311718837995</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12264,6 +13018,12 @@
       <c r="M126" t="n">
         <v>0</v>
       </c>
+      <c r="N126" t="n">
+        <v>9.363038511004451</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-8.72083887734664</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12307,6 +13067,12 @@
       <c r="M127" t="n">
         <v>0</v>
       </c>
+      <c r="N127" t="n">
+        <v>10.37570408738176</v>
+      </c>
+      <c r="O127" t="n">
+        <v>-9.648471740926862</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12350,6 +13116,12 @@
       <c r="M128" t="n">
         <v>0</v>
       </c>
+      <c r="N128" t="n">
+        <v>12.6372250503231</v>
+      </c>
+      <c r="O128" t="n">
+        <v>-11.72049839487853</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12393,6 +13165,12 @@
       <c r="M129" t="n">
         <v>0</v>
       </c>
+      <c r="N129" t="n">
+        <v>13.31746937022732</v>
+      </c>
+      <c r="O129" t="n">
+        <v>-12.3611689416523</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12436,6 +13214,12 @@
       <c r="M130" t="n">
         <v>0</v>
       </c>
+      <c r="N130" t="n">
+        <v>17.50918753896387</v>
+      </c>
+      <c r="O130" t="n">
+        <v>-16.36631545434526</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12479,6 +13263,12 @@
       <c r="M131" t="n">
         <v>0</v>
       </c>
+      <c r="N131" t="n">
+        <v>18.70479938363326</v>
+      </c>
+      <c r="O131" t="n">
+        <v>-17.52393287431894</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12522,6 +13312,12 @@
       <c r="M132" t="n">
         <v>0</v>
       </c>
+      <c r="N132" t="n">
+        <v>3.135533906065512</v>
+      </c>
+      <c r="O132" t="n">
+        <v>-3.01780046067064</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12565,6 +13361,12 @@
       <c r="M133" t="n">
         <v>0</v>
       </c>
+      <c r="N133" t="n">
+        <v>3.818355046719797</v>
+      </c>
+      <c r="O133" t="n">
+        <v>-3.642537571457864</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12608,6 +13410,12 @@
       <c r="M134" t="n">
         <v>0</v>
       </c>
+      <c r="N134" t="n">
+        <v>3.590748000806419</v>
+      </c>
+      <c r="O134" t="n">
+        <v>-3.434291868884014</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12651,6 +13459,12 @@
       <c r="M135" t="n">
         <v>0</v>
       </c>
+      <c r="N135" t="n">
+        <v>4.959679878146953</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-4.687226718185606</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12694,6 +13508,12 @@
       <c r="M136" t="n">
         <v>0</v>
       </c>
+      <c r="N136" t="n">
+        <v>5.189121000938723</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-4.897401854415585</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12737,6 +13557,12 @@
       <c r="M137" t="n">
         <v>0</v>
       </c>
+      <c r="N137" t="n">
+        <v>5.648003246522279</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-5.317752126875545</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12780,6 +13606,12 @@
       <c r="M138" t="n">
         <v>0</v>
       </c>
+      <c r="N138" t="n">
+        <v>10.69570802978191</v>
+      </c>
+      <c r="O138" t="n">
+        <v>-9.941605210030776</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12823,6 +13655,12 @@
       <c r="M139" t="n">
         <v>0</v>
       </c>
+      <c r="N139" t="n">
+        <v>11.61347252931251</v>
+      </c>
+      <c r="O139" t="n">
+        <v>-10.78230576374905</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12866,6 +13704,12 @@
       <c r="M140" t="n">
         <v>0</v>
       </c>
+      <c r="N140" t="n">
+        <v>14.51373868916084</v>
+      </c>
+      <c r="O140" t="n">
+        <v>-13.49021646585321</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12909,6 +13753,12 @@
       <c r="M141" t="n">
         <v>0</v>
       </c>
+      <c r="N141" t="n">
+        <v>14.82489071709765</v>
+      </c>
+      <c r="O141" t="n">
+        <v>-13.78635079622434</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12952,6 +13802,12 @@
       <c r="M142" t="n">
         <v>0</v>
       </c>
+      <c r="N142" t="n">
+        <v>4.546697587757196</v>
+      </c>
+      <c r="O142" t="n">
+        <v>-4.308923813502774</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12995,6 +13851,12 @@
       <c r="M143" t="n">
         <v>0</v>
       </c>
+      <c r="N143" t="n">
+        <v>6.726376511803648</v>
+      </c>
+      <c r="O143" t="n">
+        <v>-6.305575254700909</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13038,6 +13900,12 @@
       <c r="M144" t="n">
         <v>0</v>
       </c>
+      <c r="N144" t="n">
+        <v>10.81042859222322</v>
+      </c>
+      <c r="O144" t="n">
+        <v>-10.04669277924556</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13081,6 +13949,12 @@
       <c r="M145" t="n">
         <v>0</v>
       </c>
+      <c r="N145" t="n">
+        <v>28.49769451589967</v>
+      </c>
+      <c r="O145" t="n">
+        <v>-27.00645264853131</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13124,6 +13998,12 @@
       <c r="M146" t="n">
         <v>0</v>
       </c>
+      <c r="N146" t="n">
+        <v>2.679650138921736</v>
+      </c>
+      <c r="O146" t="n">
+        <v>-2.600696490699615</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13167,6 +14047,12 @@
       <c r="M147" t="n">
         <v>0</v>
       </c>
+      <c r="N147" t="n">
+        <v>3.828974330002182</v>
+      </c>
+      <c r="O147" t="n">
+        <v>-3.652253527142086</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13210,6 +14096,12 @@
       <c r="M148" t="n">
         <v>0</v>
       </c>
+      <c r="N148" t="n">
+        <v>6.001953191642652</v>
+      </c>
+      <c r="O148" t="n">
+        <v>-5.641981178377453</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13253,6 +14145,12 @@
       <c r="M149" t="n">
         <v>0</v>
       </c>
+      <c r="N149" t="n">
+        <v>8.734317854585013</v>
+      </c>
+      <c r="O149" t="n">
+        <v>-8.144911388043816</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13296,6 +14194,12 @@
       <c r="M150" t="n">
         <v>0</v>
       </c>
+      <c r="N150" t="n">
+        <v>11.82651630313832</v>
+      </c>
+      <c r="O150" t="n">
+        <v>-10.97746042348277</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13339,6 +14243,12 @@
       <c r="M151" t="n">
         <v>0</v>
       </c>
+      <c r="N151" t="n">
+        <v>15.31847804174633</v>
+      </c>
+      <c r="O151" t="n">
+        <v>-14.26012616864601</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13382,6 +14292,12 @@
       <c r="M152" t="n">
         <v>0</v>
       </c>
+      <c r="N152" t="n">
+        <v>22.32588857018945</v>
+      </c>
+      <c r="O152" t="n">
+        <v>-21.03026821298928</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13425,6 +14341,12 @@
       <c r="M153" t="n">
         <v>0</v>
       </c>
+      <c r="N153" t="n">
+        <v>32.51385910549366</v>
+      </c>
+      <c r="O153" t="n">
+        <v>-30.84431764133361</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13468,6 +14390,12 @@
       <c r="M154" t="n">
         <v>0</v>
       </c>
+      <c r="N154" t="n">
+        <v>6.336326603979133</v>
+      </c>
+      <c r="O154" t="n">
+        <v>-5.948277524079378</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13511,6 +14439,12 @@
       <c r="M155" t="n">
         <v>0</v>
       </c>
+      <c r="N155" t="n">
+        <v>24.99125103416344</v>
+      </c>
+      <c r="O155" t="n">
+        <v>-23.61093640059752</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13554,6 +14488,12 @@
       <c r="M156" t="n">
         <v>0</v>
       </c>
+      <c r="N156" t="n">
+        <v>22.08661487919257</v>
+      </c>
+      <c r="O156" t="n">
+        <v>-20.79860443285427</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13597,6 +14537,12 @@
       <c r="M157" t="n">
         <v>0</v>
       </c>
+      <c r="N157" t="n">
+        <v>21.08116390247194</v>
+      </c>
+      <c r="O157" t="n">
+        <v>-19.82510490555845</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13640,6 +14586,12 @@
       <c r="M158" t="n">
         <v>0</v>
       </c>
+      <c r="N158" t="n">
+        <v>22.07281447895515</v>
+      </c>
+      <c r="O158" t="n">
+        <v>-20.64370893205882</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13683,6 +14635,12 @@
       <c r="M159" t="n">
         <v>0</v>
       </c>
+      <c r="N159" t="n">
+        <v>4.89084753380612</v>
+      </c>
+      <c r="O159" t="n">
+        <v>-4.624174169423199</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13726,6 +14684,12 @@
       <c r="M160" t="n">
         <v>0</v>
       </c>
+      <c r="N160" t="n">
+        <v>7.483532281424743</v>
+      </c>
+      <c r="O160" t="n">
+        <v>-6.999153272016787</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13769,6 +14733,12 @@
       <c r="M161" t="n">
         <v>0</v>
       </c>
+      <c r="N161" t="n">
+        <v>10.74159625475842</v>
+      </c>
+      <c r="O161" t="n">
+        <v>-9.983640237716688</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13812,6 +14782,12 @@
       <c r="M162" t="n">
         <v>0</v>
       </c>
+      <c r="N162" t="n">
+        <v>14.0226043405804</v>
+      </c>
+      <c r="O162" t="n">
+        <v>-12.98914471725955</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13855,6 +14831,12 @@
       <c r="M163" t="n">
         <v>0</v>
       </c>
+      <c r="N163" t="n">
+        <v>8.00422542851997</v>
+      </c>
+      <c r="O163" t="n">
+        <v>-7.476124234942619</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13898,6 +14880,12 @@
       <c r="M164" t="n">
         <v>0</v>
       </c>
+      <c r="N164" t="n">
+        <v>8.698729892900882</v>
+      </c>
+      <c r="O164" t="n">
+        <v>-8.112311718837997</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -13941,6 +14929,12 @@
       <c r="M165" t="n">
         <v>0</v>
       </c>
+      <c r="N165" t="n">
+        <v>9.363038511004405</v>
+      </c>
+      <c r="O165" t="n">
+        <v>-8.720838877346621</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13984,6 +14978,12 @@
       <c r="M166" t="n">
         <v>0</v>
       </c>
+      <c r="N166" t="n">
+        <v>10.37570408738172</v>
+      </c>
+      <c r="O166" t="n">
+        <v>-9.648471740926844</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14027,6 +15027,12 @@
       <c r="M167" t="n">
         <v>0</v>
       </c>
+      <c r="N167" t="n">
+        <v>12.63425519105962</v>
+      </c>
+      <c r="O167" t="n">
+        <v>-11.71737412757849</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14070,6 +15076,12 @@
       <c r="M168" t="n">
         <v>0</v>
       </c>
+      <c r="N168" t="n">
+        <v>13.18544921040957</v>
+      </c>
+      <c r="O168" t="n">
+        <v>-12.22228482908276</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14113,6 +15125,12 @@
       <c r="M169" t="n">
         <v>0</v>
       </c>
+      <c r="N169" t="n">
+        <v>16.46243772330768</v>
+      </c>
+      <c r="O169" t="n">
+        <v>-15.2651433346441</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14156,6 +15174,12 @@
       <c r="M170" t="n">
         <v>0</v>
       </c>
+      <c r="N170" t="n">
+        <v>17.39495561426811</v>
+      </c>
+      <c r="O170" t="n">
+        <v>-16.14598809857999</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14199,6 +15223,12 @@
       <c r="M171" t="n">
         <v>0</v>
       </c>
+      <c r="N171" t="n">
+        <v>3.135533917722148</v>
+      </c>
+      <c r="O171" t="n">
+        <v>-3.017800472933333</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -14242,6 +15272,12 @@
       <c r="M172" t="n">
         <v>0</v>
       </c>
+      <c r="N172" t="n">
+        <v>3.818355059775404</v>
+      </c>
+      <c r="O172" t="n">
+        <v>-3.642537585192254</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14285,6 +15321,12 @@
       <c r="M173" t="n">
         <v>0</v>
       </c>
+      <c r="N173" t="n">
+        <v>3.590748012424329</v>
+      </c>
+      <c r="O173" t="n">
+        <v>-3.434291881105947</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -14328,6 +15370,12 @@
       <c r="M174" t="n">
         <v>0</v>
       </c>
+      <c r="N174" t="n">
+        <v>4.959679907715533</v>
+      </c>
+      <c r="O174" t="n">
+        <v>-4.687226749291509</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -14371,6 +15419,12 @@
       <c r="M175" t="n">
         <v>0</v>
       </c>
+      <c r="N175" t="n">
+        <v>5.18912103259819</v>
+      </c>
+      <c r="O175" t="n">
+        <v>-4.897401887721085</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -14414,6 +15468,12 @@
       <c r="M176" t="n">
         <v>0</v>
       </c>
+      <c r="N176" t="n">
+        <v>5.648003282363511</v>
+      </c>
+      <c r="O176" t="n">
+        <v>-5.317752164580221</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -14457,6 +15517,12 @@
       <c r="M177" t="n">
         <v>0</v>
       </c>
+      <c r="N177" t="n">
+        <v>10.6957080297819</v>
+      </c>
+      <c r="O177" t="n">
+        <v>-9.941605210030776</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -14500,6 +15566,12 @@
       <c r="M178" t="n">
         <v>0</v>
       </c>
+      <c r="N178" t="n">
+        <v>11.61347252931252</v>
+      </c>
+      <c r="O178" t="n">
+        <v>-10.78230576374906</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -14543,6 +15615,12 @@
       <c r="M179" t="n">
         <v>0</v>
       </c>
+      <c r="N179" t="n">
+        <v>14.13732490302177</v>
+      </c>
+      <c r="O179" t="n">
+        <v>-13.09423228647434</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -14586,6 +15664,12 @@
       <c r="M180" t="n">
         <v>0</v>
       </c>
+      <c r="N180" t="n">
+        <v>14.36676602790435</v>
+      </c>
+      <c r="O180" t="n">
+        <v>-13.3044074249039</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14629,6 +15713,12 @@
       <c r="M181" t="n">
         <v>0</v>
       </c>
+      <c r="N181" t="n">
+        <v>4.546697611298897</v>
+      </c>
+      <c r="O181" t="n">
+        <v>-4.30892383826844</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -14672,6 +15762,12 @@
       <c r="M182" t="n">
         <v>0</v>
       </c>
+      <c r="N182" t="n">
+        <v>6.726376569311976</v>
+      </c>
+      <c r="O182" t="n">
+        <v>-6.305575315199206</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14715,6 +15811,12 @@
       <c r="M183" t="n">
         <v>0</v>
       </c>
+      <c r="N183" t="n">
+        <v>10.81042859222325</v>
+      </c>
+      <c r="O183" t="n">
+        <v>-10.04669277924556</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -14758,6 +15860,12 @@
       <c r="M184" t="n">
         <v>0</v>
       </c>
+      <c r="N184" t="n">
+        <v>26.72938400214406</v>
+      </c>
+      <c r="O184" t="n">
+        <v>-25.14620466224312</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -14801,6 +15909,12 @@
       <c r="M185" t="n">
         <v>0</v>
       </c>
+      <c r="N185" t="n">
+        <v>2.679650149181638</v>
+      </c>
+      <c r="O185" t="n">
+        <v>-2.600696501492973</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -14844,6 +15958,12 @@
       <c r="M186" t="n">
         <v>0</v>
       </c>
+      <c r="N186" t="n">
+        <v>3.828974330002102</v>
+      </c>
+      <c r="O186" t="n">
+        <v>-3.652253527142033</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -14887,6 +16007,12 @@
       <c r="M187" t="n">
         <v>0</v>
       </c>
+      <c r="N187" t="n">
+        <v>6.001953191642634</v>
+      </c>
+      <c r="O187" t="n">
+        <v>-5.641981178377448</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -14930,6 +16056,12 @@
       <c r="M188" t="n">
         <v>0</v>
       </c>
+      <c r="N188" t="n">
+        <v>8.734317854585026</v>
+      </c>
+      <c r="O188" t="n">
+        <v>-8.14491138804382</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -14973,6 +16105,12 @@
       <c r="M189" t="n">
         <v>0</v>
       </c>
+      <c r="N189" t="n">
+        <v>11.8265163031383</v>
+      </c>
+      <c r="O189" t="n">
+        <v>-10.97746042348277</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -15016,6 +16154,12 @@
       <c r="M190" t="n">
         <v>0</v>
       </c>
+      <c r="N190" t="n">
+        <v>14.70123276362196</v>
+      </c>
+      <c r="O190" t="n">
+        <v>-13.6107892582195</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -15059,6 +16203,12 @@
       <c r="M191" t="n">
         <v>0</v>
       </c>
+      <c r="N191" t="n">
+        <v>20.6585137822089</v>
+      </c>
+      <c r="O191" t="n">
+        <v>-19.27620377260924</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -15102,6 +16252,12 @@
       <c r="M192" t="n">
         <v>0</v>
       </c>
+      <c r="N192" t="n">
+        <v>33.21948023565858</v>
+      </c>
+      <c r="O192" t="n">
+        <v>-31.42158017157451</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -15145,6 +16301,12 @@
       <c r="M193" t="n">
         <v>0</v>
       </c>
+      <c r="N193" t="n">
+        <v>6.336326603979183</v>
+      </c>
+      <c r="O193" t="n">
+        <v>-5.9482775240794</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15188,6 +16350,12 @@
       <c r="M194" t="n">
         <v>0</v>
       </c>
+      <c r="N194" t="n">
+        <v>23.2827892372086</v>
+      </c>
+      <c r="O194" t="n">
+        <v>-21.8136487677341</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -15231,6 +16399,12 @@
       <c r="M195" t="n">
         <v>0</v>
       </c>
+      <c r="N195" t="n">
+        <v>20.42284890011524</v>
+      </c>
+      <c r="O195" t="n">
+        <v>-19.04833642949304</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -15274,6 +16448,12 @@
       <c r="M196" t="n">
         <v>0</v>
       </c>
+      <c r="N196" t="n">
+        <v>19.49083126555582</v>
+      </c>
+      <c r="O196" t="n">
+        <v>-18.15208816877024</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -15317,6 +16497,12 @@
       <c r="M197" t="n">
         <v>0</v>
       </c>
+      <c r="N197" t="n">
+        <v>7.736105329481583</v>
+      </c>
+      <c r="O197" t="n">
+        <v>-9.142171602472363</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15360,6 +16546,12 @@
       <c r="M198" t="n">
         <v>0</v>
       </c>
+      <c r="N198" t="n">
+        <v>4.202639471589306</v>
+      </c>
+      <c r="O198" t="n">
+        <v>-4.086525541101987</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -15403,6 +16595,12 @@
       <c r="M199" t="n">
         <v>0</v>
       </c>
+      <c r="N199" t="n">
+        <v>4.98689347468397</v>
+      </c>
+      <c r="O199" t="n">
+        <v>-4.831058675298054</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -15446,6 +16644,12 @@
       <c r="M200" t="n">
         <v>0</v>
       </c>
+      <c r="N200" t="n">
+        <v>6.366641202684748</v>
+      </c>
+      <c r="O200" t="n">
+        <v>-6.367013136108619</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -15489,6 +16693,12 @@
       <c r="M201" t="n">
         <v>0</v>
       </c>
+      <c r="N201" t="n">
+        <v>6.851382176309546</v>
+      </c>
+      <c r="O201" t="n">
+        <v>-7.349312537015606</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15532,6 +16742,12 @@
       <c r="M202" t="n">
         <v>0</v>
       </c>
+      <c r="N202" t="n">
+        <v>5.22775221085307</v>
+      </c>
+      <c r="O202" t="n">
+        <v>-5.064961938882522</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -15575,6 +16791,12 @@
       <c r="M203" t="n">
         <v>0</v>
       </c>
+      <c r="N203" t="n">
+        <v>5.724496923389295</v>
+      </c>
+      <c r="O203" t="n">
+        <v>-5.553231358599386</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -15618,6 +16840,12 @@
       <c r="M204" t="n">
         <v>0</v>
       </c>
+      <c r="N204" t="n">
+        <v>6.089233800366006</v>
+      </c>
+      <c r="O204" t="n">
+        <v>-5.91048564519383</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -15661,6 +16889,12 @@
       <c r="M205" t="n">
         <v>0</v>
       </c>
+      <c r="N205" t="n">
+        <v>6.312579215912367</v>
+      </c>
+      <c r="O205" t="n">
+        <v>-6.257465891254606</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -15704,6 +16938,12 @@
       <c r="M206" t="n">
         <v>0</v>
       </c>
+      <c r="N206" t="n">
+        <v>6.646263702015967</v>
+      </c>
+      <c r="O206" t="n">
+        <v>-6.933654239437585</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -15747,6 +16987,12 @@
       <c r="M207" t="n">
         <v>0</v>
       </c>
+      <c r="N207" t="n">
+        <v>6.727698606362676</v>
+      </c>
+      <c r="O207" t="n">
+        <v>-7.098676395839383</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -15790,6 +17036,12 @@
       <c r="M208" t="n">
         <v>0</v>
       </c>
+      <c r="N208" t="n">
+        <v>7.16725770633644</v>
+      </c>
+      <c r="O208" t="n">
+        <v>-7.989412267952345</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15833,6 +17085,12 @@
       <c r="M209" t="n">
         <v>0</v>
       </c>
+      <c r="N209" t="n">
+        <v>7.276093169536514</v>
+      </c>
+      <c r="O209" t="n">
+        <v>-8.209959746632958</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15876,6 +17134,12 @@
       <c r="M210" t="n">
         <v>0</v>
       </c>
+      <c r="N210" t="n">
+        <v>3.756730528001784</v>
+      </c>
+      <c r="O210" t="n">
+        <v>-3.671220759686101</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -15919,6 +17183,12 @@
       <c r="M211" t="n">
         <v>0</v>
       </c>
+      <c r="N211" t="n">
+        <v>4.118333806722795</v>
+      </c>
+      <c r="O211" t="n">
+        <v>-4.020170606307655</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15962,6 +17232,12 @@
       <c r="M212" t="n">
         <v>0</v>
       </c>
+      <c r="N212" t="n">
+        <v>4.100191538830246</v>
+      </c>
+      <c r="O212" t="n">
+        <v>-4.005855915371555</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -16005,6 +17281,12 @@
       <c r="M213" t="n">
         <v>0</v>
       </c>
+      <c r="N213" t="n">
+        <v>4.208071301368796</v>
+      </c>
+      <c r="O213" t="n">
+        <v>-4.090809536229036</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -16048,6 +17330,12 @@
       <c r="M214" t="n">
         <v>0</v>
       </c>
+      <c r="N214" t="n">
+        <v>4.226181792351633</v>
+      </c>
+      <c r="O214" t="n">
+        <v>-4.105093733283121</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -16091,6 +17379,12 @@
       <c r="M215" t="n">
         <v>0</v>
       </c>
+      <c r="N215" t="n">
+        <v>4.26240277431734</v>
+      </c>
+      <c r="O215" t="n">
+        <v>-4.133662127391322</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -16134,6 +17428,12 @@
       <c r="M216" t="n">
         <v>0</v>
       </c>
+      <c r="N216" t="n">
+        <v>6.359857627380754</v>
+      </c>
+      <c r="O216" t="n">
+        <v>-6.353272079759487</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -16177,6 +17477,12 @@
       <c r="M217" t="n">
         <v>0</v>
       </c>
+      <c r="N217" t="n">
+        <v>6.495450660239075</v>
+      </c>
+      <c r="O217" t="n">
+        <v>-6.628041896667756</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -16220,6 +17526,12 @@
       <c r="M218" t="n">
         <v>0</v>
       </c>
+      <c r="N218" t="n">
+        <v>6.868326633521686</v>
+      </c>
+      <c r="O218" t="n">
+        <v>-7.383655710161973</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -16263,6 +17575,12 @@
       <c r="M219" t="n">
         <v>0</v>
       </c>
+      <c r="N219" t="n">
+        <v>6.902224838688969</v>
+      </c>
+      <c r="O219" t="n">
+        <v>-7.452348129696821</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -16306,6 +17624,12 @@
       <c r="M220" t="n">
         <v>0</v>
       </c>
+      <c r="N220" t="n">
+        <v>4.175470753170086</v>
+      </c>
+      <c r="O220" t="n">
+        <v>-4.065096384535306</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -16349,6 +17673,12 @@
       <c r="M221" t="n">
         <v>0</v>
       </c>
+      <c r="N221" t="n">
+        <v>4.605369815175474</v>
+      </c>
+      <c r="O221" t="n">
+        <v>-4.460114216129598</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -16392,6 +17722,12 @@
       <c r="M222" t="n">
         <v>0</v>
       </c>
+      <c r="N222" t="n">
+        <v>6.376806796402597</v>
+      </c>
+      <c r="O222" t="n">
+        <v>-6.387618336097081</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16435,6 +17771,12 @@
       <c r="M223" t="n">
         <v>0</v>
       </c>
+      <c r="N223" t="n">
+        <v>8.166627939295156</v>
+      </c>
+      <c r="O223" t="n">
+        <v>-10.01457541297646</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -16478,6 +17820,12 @@
       <c r="M224" t="n">
         <v>0.3375606178649292</v>
       </c>
+      <c r="N224" t="n">
+        <v>2.869665809908673</v>
+      </c>
+      <c r="O224" t="n">
+        <v>-2.80053196002452</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -16521,6 +17869,12 @@
       <c r="M225" t="n">
         <v>0</v>
       </c>
+      <c r="N225" t="n">
+        <v>4.119180312121462</v>
+      </c>
+      <c r="O225" t="n">
+        <v>-4.020838529188825</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -16564,6 +17918,12 @@
       <c r="M226" t="n">
         <v>0</v>
       </c>
+      <c r="N226" t="n">
+        <v>4.299756314012812</v>
+      </c>
+      <c r="O226" t="n">
+        <v>-4.16529637156699</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -16607,6 +17967,12 @@
       <c r="M227" t="n">
         <v>0</v>
       </c>
+      <c r="N227" t="n">
+        <v>5.744037936957122</v>
+      </c>
+      <c r="O227" t="n">
+        <v>-5.572371287493528</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -16650,6 +18016,12 @@
       <c r="M228" t="n">
         <v>0</v>
       </c>
+      <c r="N228" t="n">
+        <v>6.526930532598812</v>
+      </c>
+      <c r="O228" t="n">
+        <v>-6.69182789286347</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -16693,6 +18065,12 @@
       <c r="M229" t="n">
         <v>0</v>
       </c>
+      <c r="N229" t="n">
+        <v>6.951644604692782</v>
+      </c>
+      <c r="O229" t="n">
+        <v>-7.552487333254978</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -16736,6 +18114,12 @@
       <c r="M230" t="n">
         <v>0</v>
       </c>
+      <c r="N230" t="n">
+        <v>7.605372153284932</v>
+      </c>
+      <c r="O230" t="n">
+        <v>-8.877220632457867</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -16779,6 +18163,12 @@
       <c r="M231" t="n">
         <v>0</v>
       </c>
+      <c r="N231" t="n">
+        <v>8.766633673885826</v>
+      </c>
+      <c r="O231" t="n">
+        <v>-11.2304361405636</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -16822,6 +18212,12 @@
       <c r="M232" t="n">
         <v>0</v>
       </c>
+      <c r="N232" t="n">
+        <v>4.357148485601385</v>
+      </c>
+      <c r="O232" t="n">
+        <v>-4.217682151379345</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -16865,6 +18261,12 @@
       <c r="M233" t="n">
         <v>0</v>
       </c>
+      <c r="N233" t="n">
+        <v>7.848009639494681</v>
+      </c>
+      <c r="O233" t="n">
+        <v>-9.36888290240706</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16908,6 +18310,12 @@
       <c r="M234" t="n">
         <v>0</v>
       </c>
+      <c r="N234" t="n">
+        <v>7.583602030916892</v>
+      </c>
+      <c r="O234" t="n">
+        <v>-8.833080978330335</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16951,6 +18359,12 @@
       <c r="M235" t="n">
         <v>0</v>
       </c>
+      <c r="N235" t="n">
+        <v>7.492076320255349</v>
+      </c>
+      <c r="O235" t="n">
+        <v>-8.647611081534539</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -16994,6 +18408,12 @@
       <c r="M236" t="n">
         <v>0</v>
       </c>
+      <c r="N236" t="n">
+        <v>6.356313485052497</v>
+      </c>
+      <c r="O236" t="n">
+        <v>-8.461088445767071</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -17037,6 +18457,12 @@
       <c r="M237" t="n">
         <v>0.3238730869793933</v>
       </c>
+      <c r="N237" t="n">
+        <v>4.554346411407843</v>
+      </c>
+      <c r="O237" t="n">
+        <v>-4.436738896221634</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -17080,6 +18506,12 @@
       <c r="M238" t="n">
         <v>0</v>
       </c>
+      <c r="N238" t="n">
+        <v>5.096943135536347</v>
+      </c>
+      <c r="O238" t="n">
+        <v>-4.992698520072409</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -17123,6 +18555,12 @@
       <c r="M239" t="n">
         <v>0</v>
       </c>
+      <c r="N239" t="n">
+        <v>5.424477122394571</v>
+      </c>
+      <c r="O239" t="n">
+        <v>-5.894737730476079</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -17166,6 +18604,12 @@
       <c r="M240" t="n">
         <v>0</v>
       </c>
+      <c r="N240" t="n">
+        <v>5.754311815166837</v>
+      </c>
+      <c r="O240" t="n">
+        <v>-6.803125286854186</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -17209,6 +18653,12 @@
       <c r="M241" t="n">
         <v>0</v>
       </c>
+      <c r="N241" t="n">
+        <v>5.149284387495756</v>
+      </c>
+      <c r="O241" t="n">
+        <v>-5.136856619017934</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -17252,6 +18702,12 @@
       <c r="M242" t="n">
         <v>0</v>
       </c>
+      <c r="N242" t="n">
+        <v>5.219102897717571</v>
+      </c>
+      <c r="O242" t="n">
+        <v>-5.329139465541829</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -17295,6 +18751,12 @@
       <c r="M243" t="n">
         <v>0</v>
       </c>
+      <c r="N243" t="n">
+        <v>5.285885820538444</v>
+      </c>
+      <c r="O243" t="n">
+        <v>-5.513062188303817</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -17338,6 +18800,12 @@
       <c r="M244" t="n">
         <v>0</v>
       </c>
+      <c r="N244" t="n">
+        <v>5.387689056545868</v>
+      </c>
+      <c r="O244" t="n">
+        <v>-5.793432192514165</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -17381,6 +18849,12 @@
       <c r="M245" t="n">
         <v>0</v>
       </c>
+      <c r="N245" t="n">
+        <v>5.614741122307901</v>
+      </c>
+      <c r="O245" t="n">
+        <v>-6.418742262510587</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -17424,6 +18898,12 @@
       <c r="M246" t="n">
         <v>0</v>
       </c>
+      <c r="N246" t="n">
+        <v>5.670152638356957</v>
+      </c>
+      <c r="O246" t="n">
+        <v>-6.571347696259709</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -17467,6 +18947,12 @@
       <c r="M247" t="n">
         <v>0</v>
       </c>
+      <c r="N247" t="n">
+        <v>5.969245961031107</v>
+      </c>
+      <c r="O247" t="n">
+        <v>-7.395062142147435</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -17510,6 +18996,12 @@
       <c r="M248" t="n">
         <v>0</v>
       </c>
+      <c r="N248" t="n">
+        <v>6.043301896433717</v>
+      </c>
+      <c r="O248" t="n">
+        <v>-7.599015019628822</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -17553,6 +19045,12 @@
       <c r="M249" t="n">
         <v>0.6283683208921431</v>
       </c>
+      <c r="N249" t="n">
+        <v>3.6332214099944</v>
+      </c>
+      <c r="O249" t="n">
+        <v>-3.541284579272359</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17596,6 +19094,12 @@
       <c r="M250" t="n">
         <v>0.6913136565659241</v>
       </c>
+      <c r="N250" t="n">
+        <v>4.470237198284012</v>
+      </c>
+      <c r="O250" t="n">
+        <v>-4.365864421431868</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -17639,6 +19143,12 @@
       <c r="M251" t="n">
         <v>0.6725886030894304</v>
       </c>
+      <c r="N251" t="n">
+        <v>4.452081970654716</v>
+      </c>
+      <c r="O251" t="n">
+        <v>-4.350536254731407</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -17682,6 +19192,12 @@
       <c r="M252" t="n">
         <v>0.2627814386525849</v>
       </c>
+      <c r="N252" t="n">
+        <v>4.559620056281939</v>
+      </c>
+      <c r="O252" t="n">
+        <v>-4.441171857510366</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -17725,6 +19241,12 @@
       <c r="M253" t="n">
         <v>0.05913627140311356</v>
       </c>
+      <c r="N253" t="n">
+        <v>4.577189558155525</v>
+      </c>
+      <c r="O253" t="n">
+        <v>-4.455939473631306</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -17768,6 +19290,12 @@
       <c r="M254" t="n">
         <v>0</v>
       </c>
+      <c r="N254" t="n">
+        <v>4.954395110114107</v>
+      </c>
+      <c r="O254" t="n">
+        <v>-4.827806968060559</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -17811,6 +19339,12 @@
       <c r="M255" t="n">
         <v>0</v>
       </c>
+      <c r="N255" t="n">
+        <v>5.419864091593493</v>
+      </c>
+      <c r="O255" t="n">
+        <v>-5.882033033186937</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -17854,6 +19388,12 @@
       <c r="M256" t="n">
         <v>0</v>
       </c>
+      <c r="N256" t="n">
+        <v>5.512127059793358</v>
+      </c>
+      <c r="O256" t="n">
+        <v>-6.136128498214996</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -17897,6 +19437,12 @@
       <c r="M257" t="n">
         <v>0</v>
       </c>
+      <c r="N257" t="n">
+        <v>5.765837906533005</v>
+      </c>
+      <c r="O257" t="n">
+        <v>-6.834882565858864</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -17940,6 +19486,12 @@
       <c r="M258" t="n">
         <v>0</v>
       </c>
+      <c r="N258" t="n">
+        <v>5.788903539818616</v>
+      </c>
+      <c r="O258" t="n">
+        <v>-6.898406357293967</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -17983,6 +19535,12 @@
       <c r="M259" t="n">
         <v>0.6293772607976786</v>
       </c>
+      <c r="N259" t="n">
+        <v>4.528046152457331</v>
+      </c>
+      <c r="O259" t="n">
+        <v>-4.414639145256292</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -18026,6 +19584,12 @@
       <c r="M260" t="n">
         <v>0</v>
       </c>
+      <c r="N260" t="n">
+        <v>5.020397112801337</v>
+      </c>
+      <c r="O260" t="n">
+        <v>-4.882368554477498</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -18069,6 +19633,12 @@
       <c r="M261" t="n">
         <v>0</v>
       </c>
+      <c r="N261" t="n">
+        <v>5.431391246677784</v>
+      </c>
+      <c r="O261" t="n">
+        <v>-5.913791054159697</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -18112,6 +19682,12 @@
       <c r="M262" t="n">
         <v>0</v>
       </c>
+      <c r="N262" t="n">
+        <v>6.649251661250468</v>
+      </c>
+      <c r="O262" t="n">
+        <v>-9.267843777739941</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -18155,6 +19731,12 @@
       <c r="M263" t="n">
         <v>0</v>
       </c>
+      <c r="N263" t="n">
+        <v>2.713538948587841</v>
+      </c>
+      <c r="O263" t="n">
+        <v>-2.636280824525355</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -18198,6 +19780,12 @@
       <c r="M264" t="n">
         <v>0.6923141583300793</v>
       </c>
+      <c r="N264" t="n">
+        <v>4.471533560250029</v>
+      </c>
+      <c r="O264" t="n">
+        <v>-4.367009750438297</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -18241,6 +19829,12 @@
       <c r="M265" t="n">
         <v>0</v>
       </c>
+      <c r="N265" t="n">
+        <v>4.956548326477371</v>
+      </c>
+      <c r="O265" t="n">
+        <v>-4.826130390725234</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -18284,6 +19878,12 @@
       <c r="M266" t="n">
         <v>0</v>
       </c>
+      <c r="N266" t="n">
+        <v>5.222682310760209</v>
+      </c>
+      <c r="O266" t="n">
+        <v>-5.338993682914245</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -18327,6 +19927,12 @@
       <c r="M267" t="n">
         <v>0</v>
       </c>
+      <c r="N267" t="n">
+        <v>5.533541272442346</v>
+      </c>
+      <c r="O267" t="n">
+        <v>-6.195110412822099</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -18370,6 +19976,12 @@
       <c r="M268" t="n">
         <v>0</v>
       </c>
+      <c r="N268" t="n">
+        <v>5.822530679825956</v>
+      </c>
+      <c r="O268" t="n">
+        <v>-6.991010149787389</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -18413,6 +20025,12 @@
       <c r="M269" t="n">
         <v>0</v>
       </c>
+      <c r="N269" t="n">
+        <v>6.26735189060011</v>
+      </c>
+      <c r="O269" t="n">
+        <v>-8.21606633710055</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -18456,6 +20074,12 @@
       <c r="M270" t="n">
         <v>0</v>
       </c>
+      <c r="N270" t="n">
+        <v>7.057518614844123</v>
+      </c>
+      <c r="O270" t="n">
+        <v>-10.3922184878926</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -18499,6 +20123,12 @@
       <c r="M271" t="n">
         <v>0</v>
       </c>
+      <c r="N271" t="n">
+        <v>4.980884849631377</v>
+      </c>
+      <c r="O271" t="n">
+        <v>-4.846941087927345</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -18542,6 +20172,12 @@
       <c r="M272" t="n">
         <v>0</v>
       </c>
+      <c r="N272" t="n">
+        <v>6.432429954908597</v>
+      </c>
+      <c r="O272" t="n">
+        <v>-8.670716875220533</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -18585,6 +20221,12 @@
       <c r="M273" t="n">
         <v>0</v>
       </c>
+      <c r="N273" t="n">
+        <v>6.252518327325753</v>
+      </c>
+      <c r="O273" t="n">
+        <v>-8.175231516231207</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -18628,6 +20270,12 @@
       <c r="M274" t="n">
         <v>0</v>
       </c>
+      <c r="N274" t="n">
+        <v>6.190241225470152</v>
+      </c>
+      <c r="O274" t="n">
+        <v>-8.003717353504129</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -18671,6 +20319,12 @@
       <c r="M275" t="n">
         <v>0</v>
       </c>
+      <c r="N275" t="n">
+        <v>3.427621886777548</v>
+      </c>
+      <c r="O275" t="n">
+        <v>-8.855307572127931</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -18714,6 +20368,12 @@
       <c r="M276" t="n">
         <v>0.6113338666715147</v>
       </c>
+      <c r="N276" t="n">
+        <v>4.671460257913538</v>
+      </c>
+      <c r="O276" t="n">
+        <v>-4.546298439534464</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -18757,6 +20417,12 @@
       <c r="M277" t="n">
         <v>0</v>
       </c>
+      <c r="N277" t="n">
+        <v>5.310997664726408</v>
+      </c>
+      <c r="O277" t="n">
+        <v>-5.144593463099022</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -18800,6 +20466,12 @@
       <c r="M278" t="n">
         <v>0</v>
       </c>
+      <c r="N278" t="n">
+        <v>5.323678634102603</v>
+      </c>
+      <c r="O278" t="n">
+        <v>-6.142577181504594</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -18843,6 +20515,12 @@
       <c r="M279" t="n">
         <v>0</v>
       </c>
+      <c r="N279" t="n">
+        <v>4.652560698180434</v>
+      </c>
+      <c r="O279" t="n">
+        <v>-7.102780794628841</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -18886,6 +20564,12 @@
       <c r="M280" t="n">
         <v>0</v>
       </c>
+      <c r="N280" t="n">
+        <v>5.582851787615774</v>
+      </c>
+      <c r="O280" t="n">
+        <v>-5.408883189230286</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -18929,6 +20613,12 @@
       <c r="M281" t="n">
         <v>0</v>
       </c>
+      <c r="N281" t="n">
+        <v>5.730216140604417</v>
+      </c>
+      <c r="O281" t="n">
+        <v>-5.546370472178709</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -18972,6 +20662,12 @@
       <c r="M282" t="n">
         <v>0</v>
       </c>
+      <c r="N282" t="n">
+        <v>5.605674507662043</v>
+      </c>
+      <c r="O282" t="n">
+        <v>-5.739142200171571</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -19015,6 +20711,12 @@
       <c r="M283" t="n">
         <v>0</v>
       </c>
+      <c r="N283" t="n">
+        <v>5.398538584455925</v>
+      </c>
+      <c r="O283" t="n">
+        <v>-6.035504323217737</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -19058,6 +20760,12 @@
       <c r="M284" t="n">
         <v>0</v>
       </c>
+      <c r="N284" t="n">
+        <v>4.936562707244688</v>
+      </c>
+      <c r="O284" t="n">
+        <v>-6.696481664314637</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -19101,6 +20809,12 @@
       <c r="M285" t="n">
         <v>0</v>
       </c>
+      <c r="N285" t="n">
+        <v>4.823818594353841</v>
+      </c>
+      <c r="O285" t="n">
+        <v>-6.857791610653756</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -19144,6 +20858,12 @@
       <c r="M286" t="n">
         <v>0</v>
       </c>
+      <c r="N286" t="n">
+        <v>4.215262630342854</v>
+      </c>
+      <c r="O286" t="n">
+        <v>-7.728490211502729</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -19187,6 +20907,12 @@
       <c r="M287" t="n">
         <v>0</v>
       </c>
+      <c r="N287" t="n">
+        <v>4.064583290564434</v>
+      </c>
+      <c r="O287" t="n">
+        <v>-7.944076426604594</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -19230,6 +20956,12 @@
       <c r="M288" t="n">
         <v>0</v>
       </c>
+      <c r="N288" t="n">
+        <v>3.6020695970032</v>
+      </c>
+      <c r="O288" t="n">
+        <v>-3.508592257649289</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -19273,6 +21005,12 @@
       <c r="M289" t="n">
         <v>0.5890042586699921</v>
       </c>
+      <c r="N289" t="n">
+        <v>4.465214913443627</v>
+      </c>
+      <c r="O289" t="n">
+        <v>-4.358356894015539</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -19316,6 +21054,12 @@
       <c r="M290" t="n">
         <v>0.5672791384410391</v>
       </c>
+      <c r="N290" t="n">
+        <v>4.423451408017821</v>
+      </c>
+      <c r="O290" t="n">
+        <v>-4.320534791873877</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -19359,6 +21103,12 @@
       <c r="M291" t="n">
         <v>0.588955086334021</v>
       </c>
+      <c r="N291" t="n">
+        <v>4.687663438971732</v>
+      </c>
+      <c r="O291" t="n">
+        <v>-4.561396322385892</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -19402,6 +21152,12 @@
       <c r="M292" t="n">
         <v>0.5143498651520736</v>
       </c>
+      <c r="N292" t="n">
+        <v>4.741654698046728</v>
+      </c>
+      <c r="O292" t="n">
+        <v>-4.611704141118082</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -19445,6 +21201,12 @@
       <c r="M293" t="n">
         <v>0.3651394227881692</v>
       </c>
+      <c r="N293" t="n">
+        <v>4.849637216196694</v>
+      </c>
+      <c r="O293" t="n">
+        <v>-4.712319778582449</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -19488,6 +21250,12 @@
       <c r="M294" t="n">
         <v>0</v>
       </c>
+      <c r="N294" t="n">
+        <v>5.333083315391781</v>
+      </c>
+      <c r="O294" t="n">
+        <v>-6.129155235523581</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -19531,6 +21299,12 @@
       <c r="M295" t="n">
         <v>0</v>
       </c>
+      <c r="N295" t="n">
+        <v>5.145358956428438</v>
+      </c>
+      <c r="O295" t="n">
+        <v>-6.397744039424519</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -19574,6 +21348,12 @@
       <c r="M296" t="n">
         <v>0</v>
       </c>
+      <c r="N296" t="n">
+        <v>4.629116969279226</v>
+      </c>
+      <c r="O296" t="n">
+        <v>-7.136363250152102</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -19617,6 +21397,12 @@
       <c r="M297" t="n">
         <v>0</v>
       </c>
+      <c r="N297" t="n">
+        <v>4.582185879538391</v>
+      </c>
+      <c r="O297" t="n">
+        <v>-7.203510451127334</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -19660,6 +21446,12 @@
       <c r="M298" t="n">
         <v>0.658526315166454</v>
       </c>
+      <c r="N298" t="n">
+        <v>4.598865031003041</v>
+      </c>
+      <c r="O298" t="n">
+        <v>-4.479394215954029</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -19703,6 +21495,12 @@
       <c r="M299" t="n">
         <v>0.01449699119006902</v>
       </c>
+      <c r="N299" t="n">
+        <v>5.103400525740497</v>
+      </c>
+      <c r="O299" t="n">
+        <v>-4.948770716059729</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -19746,6 +21544,12 @@
       <c r="M300" t="n">
         <v>0</v>
       </c>
+      <c r="N300" t="n">
+        <v>5.309611721321891</v>
+      </c>
+      <c r="O300" t="n">
+        <v>-6.162726379234531</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -19789,6 +21593,12 @@
       <c r="M301" t="n">
         <v>0</v>
       </c>
+      <c r="N301" t="n">
+        <v>2.831646184937091</v>
+      </c>
+      <c r="O301" t="n">
+        <v>-9.708096976169189</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -19832,6 +21642,12 @@
       <c r="M302" t="n">
         <v>0</v>
       </c>
+      <c r="N302" t="n">
+        <v>2.722991640726992</v>
+      </c>
+      <c r="O302" t="n">
+        <v>-2.64629138800097</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -19875,6 +21691,12 @@
       <c r="M303" t="n">
         <v>0.588339585421778</v>
       </c>
+      <c r="N303" t="n">
+        <v>4.460258575636602</v>
+      </c>
+      <c r="O303" t="n">
+        <v>-4.35352114058947</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -19918,6 +21740,12 @@
       <c r="M304" t="n">
         <v>0.2468295000663375</v>
       </c>
+      <c r="N304" t="n">
+        <v>4.926220632141287</v>
+      </c>
+      <c r="O304" t="n">
+        <v>-4.783529392890376</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -19961,6 +21789,12 @@
       <c r="M305" t="n">
         <v>0</v>
       </c>
+      <c r="N305" t="n">
+        <v>5.720137210351575</v>
+      </c>
+      <c r="O305" t="n">
+        <v>-5.549404897616872</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -20004,6 +21838,12 @@
       <c r="M306" t="n">
         <v>0</v>
       </c>
+      <c r="N306" t="n">
+        <v>5.087649602516058</v>
+      </c>
+      <c r="O306" t="n">
+        <v>-6.454356483561919</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -20047,6 +21887,12 @@
       <c r="M307" t="n">
         <v>0</v>
       </c>
+      <c r="N307" t="n">
+        <v>4.499646417226566</v>
+      </c>
+      <c r="O307" t="n">
+        <v>-7.29566057944692</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -20090,6 +21936,12 @@
       <c r="M308" t="n">
         <v>0</v>
       </c>
+      <c r="N308" t="n">
+        <v>3.59459062033662</v>
+      </c>
+      <c r="O308" t="n">
+        <v>-8.590597695396422</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -20133,6 +21985,12 @@
       <c r="M309" t="n">
         <v>0</v>
       </c>
+      <c r="N309" t="n">
+        <v>1.986877325725586</v>
+      </c>
+      <c r="O309" t="n">
+        <v>-10.89088417955716</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -20176,6 +22034,12 @@
       <c r="M310" t="n">
         <v>0.1381056569112792</v>
       </c>
+      <c r="N310" t="n">
+        <v>5.004906738109801</v>
+      </c>
+      <c r="O310" t="n">
+        <v>-4.856847361930715</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -20219,6 +22083,12 @@
       <c r="M311" t="n">
         <v>0</v>
       </c>
+      <c r="N311" t="n">
+        <v>3.258696043660305</v>
+      </c>
+      <c r="O311" t="n">
+        <v>-9.071189421517476</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -20262,6 +22132,12 @@
       <c r="M312" t="n">
         <v>0</v>
       </c>
+      <c r="N312" t="n">
+        <v>3.624754572441848</v>
+      </c>
+      <c r="O312" t="n">
+        <v>-8.547439642272971</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -20305,6 +22181,12 @@
       <c r="M313" t="n">
         <v>0</v>
       </c>
+      <c r="N313" t="n">
+        <v>3.751467140097029</v>
+      </c>
+      <c r="O313" t="n">
+        <v>-8.366141641765271</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -20348,6 +22230,12 @@
       <c r="M314" t="n">
         <v>0</v>
       </c>
+      <c r="N314" t="n">
+        <v>21.14126000196347</v>
+      </c>
+      <c r="O314" t="n">
+        <v>-20.12031244410722</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -20391,6 +22279,12 @@
       <c r="M315" t="n">
         <v>0</v>
       </c>
+      <c r="N315" t="n">
+        <v>4.890847570250736</v>
+      </c>
+      <c r="O315" t="n">
+        <v>-4.624174207762641</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -20434,6 +22328,12 @@
       <c r="M316" t="n">
         <v>0</v>
       </c>
+      <c r="N316" t="n">
+        <v>7.565926365719794</v>
+      </c>
+      <c r="O316" t="n">
+        <v>-7.099073857692675</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -20477,6 +22377,12 @@
       <c r="M317" t="n">
         <v>0</v>
       </c>
+      <c r="N317" t="n">
+        <v>12.79158324407541</v>
+      </c>
+      <c r="O317" t="n">
+        <v>-12.15817791818894</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -20520,6 +22426,12 @@
       <c r="M318" t="n">
         <v>0</v>
       </c>
+      <c r="N318" t="n">
+        <v>17.94421694956907</v>
+      </c>
+      <c r="O318" t="n">
+        <v>-17.15953744642518</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -20563,6 +22475,12 @@
       <c r="M319" t="n">
         <v>0</v>
       </c>
+      <c r="N319" t="n">
+        <v>8.399051377496917</v>
+      </c>
+      <c r="O319" t="n">
+        <v>-7.905479456071097</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -20606,6 +22524,12 @@
       <c r="M320" t="n">
         <v>0</v>
       </c>
+      <c r="N320" t="n">
+        <v>9.510306760156679</v>
+      </c>
+      <c r="O320" t="n">
+        <v>-8.981096434337358</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -20649,6 +22573,12 @@
       <c r="M321" t="n">
         <v>0</v>
       </c>
+      <c r="N321" t="n">
+        <v>10.57510180274305</v>
+      </c>
+      <c r="O321" t="n">
+        <v>-10.0118963581499</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -20692,6 +22622,12 @@
       <c r="M322" t="n">
         <v>0</v>
       </c>
+      <c r="N322" t="n">
+        <v>12.20329218249763</v>
+      </c>
+      <c r="O322" t="n">
+        <v>-11.58851907338434</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -20735,6 +22671,12 @@
       <c r="M323" t="n">
         <v>0</v>
       </c>
+      <c r="N323" t="n">
+        <v>15.88818931161475</v>
+      </c>
+      <c r="O323" t="n">
+        <v>-15.16111149127219</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -20778,6 +22720,12 @@
       <c r="M324" t="n">
         <v>0</v>
       </c>
+      <c r="N324" t="n">
+        <v>16.87077280974244</v>
+      </c>
+      <c r="O324" t="n">
+        <v>-16.12049838360849</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -20821,6 +22769,12 @@
       <c r="M325" t="n">
         <v>0</v>
       </c>
+      <c r="N325" t="n">
+        <v>19.05988135677438</v>
+      </c>
+      <c r="O325" t="n">
+        <v>-18.19074657333759</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -20864,6 +22818,12 @@
       <c r="M326" t="n">
         <v>0</v>
       </c>
+      <c r="N326" t="n">
+        <v>19.45808871877986</v>
+      </c>
+      <c r="O326" t="n">
+        <v>-18.55990926124682</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -20907,6 +22867,12 @@
       <c r="M327" t="n">
         <v>0</v>
       </c>
+      <c r="N327" t="n">
+        <v>3.135533904570363</v>
+      </c>
+      <c r="O327" t="n">
+        <v>-3.017800459097766</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -20950,6 +22916,12 @@
       <c r="M328" t="n">
         <v>0</v>
       </c>
+      <c r="N328" t="n">
+        <v>3.818355059775407</v>
+      </c>
+      <c r="O328" t="n">
+        <v>-3.642537585192253</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -20993,6 +22965,12 @@
       <c r="M329" t="n">
         <v>0</v>
       </c>
+      <c r="N329" t="n">
+        <v>3.590748012424314</v>
+      </c>
+      <c r="O329" t="n">
+        <v>-3.434291881105947</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -21036,6 +23014,12 @@
       <c r="M330" t="n">
         <v>0</v>
       </c>
+      <c r="N330" t="n">
+        <v>4.959679907715525</v>
+      </c>
+      <c r="O330" t="n">
+        <v>-4.68722674929151</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -21079,6 +23063,12 @@
       <c r="M331" t="n">
         <v>0</v>
       </c>
+      <c r="N331" t="n">
+        <v>5.189121032598184</v>
+      </c>
+      <c r="O331" t="n">
+        <v>-4.897401887721083</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -21122,6 +23112,12 @@
       <c r="M332" t="n">
         <v>0</v>
       </c>
+      <c r="N332" t="n">
+        <v>5.648003282363466</v>
+      </c>
+      <c r="O332" t="n">
+        <v>-5.317752164580218</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -21165,6 +23161,12 @@
       <c r="M333" t="n">
         <v>0</v>
       </c>
+      <c r="N333" t="n">
+        <v>12.71780294760471</v>
+      </c>
+      <c r="O333" t="n">
+        <v>-12.08673437399485</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -21208,6 +23210,12 @@
       <c r="M334" t="n">
         <v>0</v>
       </c>
+      <c r="N334" t="n">
+        <v>14.19342816545781</v>
+      </c>
+      <c r="O334" t="n">
+        <v>-13.51562552149142</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -21251,6 +23259,12 @@
       <c r="M335" t="n">
         <v>0</v>
       </c>
+      <c r="N335" t="n">
+        <v>18.00220148541337</v>
+      </c>
+      <c r="O335" t="n">
+        <v>-17.21298288727811</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -21294,6 +23308,12 @@
       <c r="M336" t="n">
         <v>0</v>
       </c>
+      <c r="N336" t="n">
+        <v>18.11817055710218</v>
+      </c>
+      <c r="O336" t="n">
+        <v>-17.31987376898408</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -21337,6 +23357,12 @@
       <c r="M337" t="n">
         <v>0</v>
       </c>
+      <c r="N337" t="n">
+        <v>4.546697611298884</v>
+      </c>
+      <c r="O337" t="n">
+        <v>-4.308923838268437</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -21380,6 +23406,12 @@
       <c r="M338" t="n">
         <v>0</v>
       </c>
+      <c r="N338" t="n">
+        <v>6.801648565758358</v>
+      </c>
+      <c r="O338" t="n">
+        <v>-6.384760830822205</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -21423,6 +23455,12 @@
       <c r="M339" t="n">
         <v>0</v>
       </c>
+      <c r="N339" t="n">
+        <v>12.91132792525121</v>
+      </c>
+      <c r="O339" t="n">
+        <v>-12.27487624158468</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -21466,6 +23504,12 @@
       <c r="M340" t="n">
         <v>0</v>
       </c>
+      <c r="N340" t="n">
+        <v>22.70071807283414</v>
+      </c>
+      <c r="O340" t="n">
+        <v>-21.56544171465428</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -21509,6 +23553,12 @@
       <c r="M341" t="n">
         <v>0</v>
       </c>
+      <c r="N341" t="n">
+        <v>2.679650149181642</v>
+      </c>
+      <c r="O341" t="n">
+        <v>-2.600696501492973</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -21552,6 +23602,12 @@
       <c r="M342" t="n">
         <v>0</v>
       </c>
+      <c r="N342" t="n">
+        <v>3.828974332501666</v>
+      </c>
+      <c r="O342" t="n">
+        <v>-3.652253529771574</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -21595,6 +23651,12 @@
       <c r="M343" t="n">
         <v>0</v>
       </c>
+      <c r="N343" t="n">
+        <v>6.001953240837788</v>
+      </c>
+      <c r="O343" t="n">
+        <v>-5.641981230130369</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -21638,6 +23700,12 @@
       <c r="M344" t="n">
         <v>0</v>
       </c>
+      <c r="N344" t="n">
+        <v>9.573901694723263</v>
+      </c>
+      <c r="O344" t="n">
+        <v>-9.043201471853417</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -21681,6 +23749,12 @@
       <c r="M345" t="n">
         <v>0</v>
       </c>
+      <c r="N345" t="n">
+        <v>14.54328718394571</v>
+      </c>
+      <c r="O345" t="n">
+        <v>-13.85500593916629</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -21724,6 +23798,12 @@
       <c r="M346" t="n">
         <v>0</v>
       </c>
+      <c r="N346" t="n">
+        <v>18.27084296695472</v>
+      </c>
+      <c r="O346" t="n">
+        <v>-17.45987161287227</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -21767,6 +23847,12 @@
       <c r="M347" t="n">
         <v>0</v>
       </c>
+      <c r="N347" t="n">
+        <v>20.64714719868935</v>
+      </c>
+      <c r="O347" t="n">
+        <v>-19.66165449205866</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -21810,6 +23896,12 @@
       <c r="M348" t="n">
         <v>0</v>
       </c>
+      <c r="N348" t="n">
+        <v>24.896020634013</v>
+      </c>
+      <c r="O348" t="n">
+        <v>-23.60062297784998</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -21853,6 +23945,12 @@
       <c r="M349" t="n">
         <v>0</v>
       </c>
+      <c r="N349" t="n">
+        <v>6.350890940383968</v>
+      </c>
+      <c r="O349" t="n">
+        <v>-5.963599085116259</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -21896,6 +23994,12 @@
       <c r="M350" t="n">
         <v>0</v>
       </c>
+      <c r="N350" t="n">
+        <v>21.53485117593642</v>
+      </c>
+      <c r="O350" t="n">
+        <v>-20.48461098730702</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -21939,6 +24043,12 @@
       <c r="M351" t="n">
         <v>0</v>
       </c>
+      <c r="N351" t="n">
+        <v>20.56742970829772</v>
+      </c>
+      <c r="O351" t="n">
+        <v>-19.58775144759316</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -21982,6 +24092,12 @@
       <c r="M352" t="n">
         <v>0</v>
       </c>
+      <c r="N352" t="n">
+        <v>20.23255304642282</v>
+      </c>
+      <c r="O352" t="n">
+        <v>-19.27730006846147</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -22025,6 +24141,12 @@
       <c r="M353" t="n">
         <v>0</v>
       </c>
+      <c r="N353" t="n">
+        <v>20.48685757334224</v>
+      </c>
+      <c r="O353" t="n">
+        <v>-19.41243647594205</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -22068,6 +24190,12 @@
       <c r="M354" t="n">
         <v>0</v>
       </c>
+      <c r="N354" t="n">
+        <v>4.890847504650433</v>
+      </c>
+      <c r="O354" t="n">
+        <v>-4.62417413875165</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -22111,6 +24239,12 @@
       <c r="M355" t="n">
         <v>0</v>
       </c>
+      <c r="N355" t="n">
+        <v>8.055584574949437</v>
+      </c>
+      <c r="O355" t="n">
+        <v>-7.600947537674807</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -22154,6 +24288,12 @@
       <c r="M356" t="n">
         <v>0</v>
       </c>
+      <c r="N356" t="n">
+        <v>13.11212441178835</v>
+      </c>
+      <c r="O356" t="n">
+        <v>-12.47741618727491</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -22197,6 +24337,12 @@
       <c r="M357" t="n">
         <v>0</v>
       </c>
+      <c r="N357" t="n">
+        <v>16.85492674648194</v>
+      </c>
+      <c r="O357" t="n">
+        <v>-16.05129352181165</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -22240,6 +24386,12 @@
       <c r="M358" t="n">
         <v>0</v>
       </c>
+      <c r="N358" t="n">
+        <v>8.863698255548845</v>
+      </c>
+      <c r="O358" t="n">
+        <v>-8.380282516710899</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -22283,6 +24435,12 @@
       <c r="M359" t="n">
         <v>0</v>
       </c>
+      <c r="N359" t="n">
+        <v>9.941575941618723</v>
+      </c>
+      <c r="O359" t="n">
+        <v>-9.41977544843119</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -22326,6 +24484,12 @@
       <c r="M360" t="n">
         <v>0</v>
       </c>
+      <c r="N360" t="n">
+        <v>10.97258938046819</v>
+      </c>
+      <c r="O360" t="n">
+        <v>-10.41407303529409</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -22369,6 +24533,12 @@
       <c r="M361" t="n">
         <v>0</v>
       </c>
+      <c r="N361" t="n">
+        <v>12.5442562079826</v>
+      </c>
+      <c r="O361" t="n">
+        <v>-11.92977057624362</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -22412,6 +24582,12 @@
       <c r="M362" t="n">
         <v>0</v>
       </c>
+      <c r="N362" t="n">
+        <v>15.94419580003185</v>
+      </c>
+      <c r="O362" t="n">
+        <v>-15.20542170988971</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -22455,6 +24631,12 @@
       <c r="M363" t="n">
         <v>0</v>
       </c>
+      <c r="N363" t="n">
+        <v>16.34719801407242</v>
+      </c>
+      <c r="O363" t="n">
+        <v>-15.58141980094481</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -22498,6 +24680,12 @@
       <c r="M364" t="n">
         <v>0</v>
       </c>
+      <c r="N364" t="n">
+        <v>18.15161530223794</v>
+      </c>
+      <c r="O364" t="n">
+        <v>-17.25130415269926</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -22541,6 +24729,12 @@
       <c r="M365" t="n">
         <v>0</v>
       </c>
+      <c r="N365" t="n">
+        <v>18.59839160916778</v>
+      </c>
+      <c r="O365" t="n">
+        <v>-17.66476991173955</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -22584,6 +24778,12 @@
       <c r="M366" t="n">
         <v>0</v>
       </c>
+      <c r="N366" t="n">
+        <v>3.135533896740188</v>
+      </c>
+      <c r="O366" t="n">
+        <v>-3.01780045086049</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -22627,6 +24827,12 @@
       <c r="M367" t="n">
         <v>0</v>
       </c>
+      <c r="N367" t="n">
+        <v>3.818355028441958</v>
+      </c>
+      <c r="O367" t="n">
+        <v>-3.642537552229719</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -22670,6 +24876,12 @@
       <c r="M368" t="n">
         <v>0</v>
       </c>
+      <c r="N368" t="n">
+        <v>3.590747984541375</v>
+      </c>
+      <c r="O368" t="n">
+        <v>-3.434291851773307</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -22713,6 +24925,12 @@
       <c r="M369" t="n">
         <v>0</v>
       </c>
+      <c r="N369" t="n">
+        <v>4.95967990771554</v>
+      </c>
+      <c r="O369" t="n">
+        <v>-4.687226749291509</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -22756,6 +24974,12 @@
       <c r="M370" t="n">
         <v>0</v>
       </c>
+      <c r="N370" t="n">
+        <v>5.189121032598198</v>
+      </c>
+      <c r="O370" t="n">
+        <v>-4.897401887721084</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -22799,6 +25023,12 @@
       <c r="M371" t="n">
         <v>0</v>
       </c>
+      <c r="N371" t="n">
+        <v>5.648003282363501</v>
+      </c>
+      <c r="O371" t="n">
+        <v>-5.317752164580219</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -22842,6 +25072,12 @@
       <c r="M372" t="n">
         <v>0</v>
       </c>
+      <c r="N372" t="n">
+        <v>13.04090573056464</v>
+      </c>
+      <c r="O372" t="n">
+        <v>-12.40873372981974</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -22885,6 +25121,12 @@
       <c r="M373" t="n">
         <v>0</v>
       </c>
+      <c r="N373" t="n">
+        <v>14.46528518675253</v>
+      </c>
+      <c r="O373" t="n">
+        <v>-13.782389013838</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -22928,6 +25170,12 @@
       <c r="M374" t="n">
         <v>0</v>
       </c>
+      <c r="N374" t="n">
+        <v>16.92450396389036</v>
+      </c>
+      <c r="O374" t="n">
+        <v>-16.11568323213439</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -22971,6 +25219,12 @@
       <c r="M375" t="n">
         <v>0</v>
       </c>
+      <c r="N375" t="n">
+        <v>17.06365840168198</v>
+      </c>
+      <c r="O375" t="n">
+        <v>-16.24446265564586</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -23014,6 +25268,12 @@
       <c r="M376" t="n">
         <v>0</v>
       </c>
+      <c r="N376" t="n">
+        <v>4.546697568923842</v>
+      </c>
+      <c r="O376" t="n">
+        <v>-4.308923793690242</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -23057,6 +25317,12 @@
       <c r="M377" t="n">
         <v>0</v>
       </c>
+      <c r="N377" t="n">
+        <v>6.958497923273325</v>
+      </c>
+      <c r="O377" t="n">
+        <v>-6.54976505332615</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -23100,6 +25366,12 @@
       <c r="M378" t="n">
         <v>0</v>
       </c>
+      <c r="N378" t="n">
+        <v>13.21895286974025</v>
+      </c>
+      <c r="O378" t="n">
+        <v>-12.58044033224847</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -23143,6 +25415,12 @@
       <c r="M379" t="n">
         <v>0</v>
       </c>
+      <c r="N379" t="n">
+        <v>22.25411893130628</v>
+      </c>
+      <c r="O379" t="n">
+        <v>-21.04793515262104</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -23186,6 +25464,12 @@
       <c r="M380" t="n">
         <v>0</v>
       </c>
+      <c r="N380" t="n">
+        <v>2.679650149181638</v>
+      </c>
+      <c r="O380" t="n">
+        <v>-2.600696501492974</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -23229,6 +25513,12 @@
       <c r="M381" t="n">
         <v>0</v>
       </c>
+      <c r="N381" t="n">
+        <v>3.828974316004573</v>
+      </c>
+      <c r="O381" t="n">
+        <v>-3.652253512416746</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -23272,6 +25562,12 @@
       <c r="M382" t="n">
         <v>0</v>
       </c>
+      <c r="N382" t="n">
+        <v>6.033982802548246</v>
+      </c>
+      <c r="O382" t="n">
+        <v>-5.675676063255021</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -23315,6 +25611,12 @@
       <c r="M383" t="n">
         <v>0</v>
       </c>
+      <c r="N383" t="n">
+        <v>9.998673228743028</v>
+      </c>
+      <c r="O383" t="n">
+        <v>-9.475002749506656</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -23358,6 +25660,12 @@
       <c r="M384" t="n">
         <v>0</v>
       </c>
+      <c r="N384" t="n">
+        <v>14.7977953857103</v>
+      </c>
+      <c r="O384" t="n">
+        <v>-14.10322136142804</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -23401,6 +25709,12 @@
       <c r="M385" t="n">
         <v>0</v>
       </c>
+      <c r="N385" t="n">
+        <v>17.26197258626155</v>
+      </c>
+      <c r="O385" t="n">
+        <v>-16.42781871039255</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -23444,6 +25758,12 @@
       <c r="M386" t="n">
         <v>0</v>
       </c>
+      <c r="N386" t="n">
+        <v>19.94556459046544</v>
+      </c>
+      <c r="O386" t="n">
+        <v>-18.91132866326161</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -23487,6 +25807,12 @@
       <c r="M387" t="n">
         <v>0</v>
       </c>
+      <c r="N387" t="n">
+        <v>24.71261492846257</v>
+      </c>
+      <c r="O387" t="n">
+        <v>-23.32295939613666</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -23530,6 +25856,12 @@
       <c r="M388" t="n">
         <v>0</v>
       </c>
+      <c r="N388" t="n">
+        <v>6.446662348931461</v>
+      </c>
+      <c r="O388" t="n">
+        <v>-6.064349812156907</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -23573,6 +25905,12 @@
       <c r="M389" t="n">
         <v>0</v>
       </c>
+      <c r="N389" t="n">
+        <v>20.94152966431176</v>
+      </c>
+      <c r="O389" t="n">
+        <v>-19.83303701897761</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -23616,6 +25954,12 @@
       <c r="M390" t="n">
         <v>0</v>
       </c>
+      <c r="N390" t="n">
+        <v>19.85612504953798</v>
+      </c>
+      <c r="O390" t="n">
+        <v>-18.82855751558885</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -23659,6 +26003,12 @@
       <c r="M391" t="n">
         <v>0</v>
       </c>
+      <c r="N391" t="n">
+        <v>19.48040806750085</v>
+      </c>
+      <c r="O391" t="n">
+        <v>-18.48085307210808</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -23702,6 +26052,12 @@
       <c r="M392" t="n">
         <v>0</v>
       </c>
+      <c r="N392" t="n">
+        <v>20.05844424906013</v>
+      </c>
+      <c r="O392" t="n">
+        <v>-19.00288168780766</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -23745,6 +26101,12 @@
       <c r="M393" t="n">
         <v>0</v>
       </c>
+      <c r="N393" t="n">
+        <v>4.890847570250748</v>
+      </c>
+      <c r="O393" t="n">
+        <v>-4.624174207762642</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -23788,6 +26150,12 @@
       <c r="M394" t="n">
         <v>0</v>
       </c>
+      <c r="N394" t="n">
+        <v>8.040086904039677</v>
+      </c>
+      <c r="O394" t="n">
+        <v>-7.584644116483932</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -23831,6 +26199,12 @@
       <c r="M395" t="n">
         <v>0.1400695747124546</v>
       </c>
+      <c r="N395" t="n">
+        <v>10.37778783671906</v>
+      </c>
+      <c r="O395" t="n">
+        <v>-9.757991296419169</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -23874,6 +26248,12 @@
       <c r="M396" t="n">
         <v>0</v>
       </c>
+      <c r="N396" t="n">
+        <v>13.62329157646069</v>
+      </c>
+      <c r="O396" t="n">
+        <v>-12.84920593784754</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -23917,6 +26297,12 @@
       <c r="M397" t="n">
         <v>0</v>
       </c>
+      <c r="N397" t="n">
+        <v>8.809357632484076</v>
+      </c>
+      <c r="O397" t="n">
+        <v>-8.323116632188027</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -23960,6 +26346,12 @@
       <c r="M398" t="n">
         <v>0.001592087509729255</v>
       </c>
+      <c r="N398" t="n">
+        <v>9.631683981863125</v>
+      </c>
+      <c r="O398" t="n">
+        <v>-9.108610183920257</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -24003,6 +26395,12 @@
       <c r="M399" t="n">
         <v>0.7744055028010086</v>
       </c>
+      <c r="N399" t="n">
+        <v>10.16693813779784</v>
+      </c>
+      <c r="O399" t="n">
+        <v>-9.612945636806288</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -24046,6 +26444,12 @@
       <c r="M400" t="n">
         <v>0.2996168297032779</v>
       </c>
+      <c r="N400" t="n">
+        <v>10.30512941592763</v>
+      </c>
+      <c r="O400" t="n">
+        <v>-9.703300723958932</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -24089,6 +26493,12 @@
       <c r="M401" t="n">
         <v>0</v>
       </c>
+      <c r="N401" t="n">
+        <v>12.13265598931471</v>
+      </c>
+      <c r="O401" t="n">
+        <v>-11.42451703287368</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -24132,6 +26542,12 @@
       <c r="M402" t="n">
         <v>0</v>
       </c>
+      <c r="N402" t="n">
+        <v>12.72496908882655</v>
+      </c>
+      <c r="O402" t="n">
+        <v>-11.99092185692894</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -24175,6 +26591,12 @@
       <c r="M403" t="n">
         <v>0</v>
       </c>
+      <c r="N403" t="n">
+        <v>15.92208235386597</v>
+      </c>
+      <c r="O403" t="n">
+        <v>-15.04819068630635</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -24218,6 +26640,12 @@
       <c r="M404" t="n">
         <v>0</v>
       </c>
+      <c r="N404" t="n">
+        <v>16.713692180905</v>
+      </c>
+      <c r="O404" t="n">
+        <v>-15.80517483062799</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -24261,6 +26689,12 @@
       <c r="M405" t="n">
         <v>0</v>
       </c>
+      <c r="N405" t="n">
+        <v>3.135533906065504</v>
+      </c>
+      <c r="O405" t="n">
+        <v>-3.017800460670639</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -24304,6 +26738,12 @@
       <c r="M406" t="n">
         <v>0</v>
       </c>
+      <c r="N406" t="n">
+        <v>3.818355042367937</v>
+      </c>
+      <c r="O406" t="n">
+        <v>-3.642537566879735</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -24347,6 +26787,12 @@
       <c r="M407" t="n">
         <v>0</v>
       </c>
+      <c r="N407" t="n">
+        <v>3.590747996933796</v>
+      </c>
+      <c r="O407" t="n">
+        <v>-3.434291864810036</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -24390,6 +26836,12 @@
       <c r="M408" t="n">
         <v>0</v>
       </c>
+      <c r="N408" t="n">
+        <v>4.959679870481039</v>
+      </c>
+      <c r="O408" t="n">
+        <v>-4.687226710121118</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -24433,6 +26885,12 @@
       <c r="M409" t="n">
         <v>0</v>
       </c>
+      <c r="N409" t="n">
+        <v>5.189120992730722</v>
+      </c>
+      <c r="O409" t="n">
+        <v>-4.897401845780827</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -24476,6 +26934,12 @@
       <c r="M410" t="n">
         <v>0</v>
       </c>
+      <c r="N410" t="n">
+        <v>5.648003237230123</v>
+      </c>
+      <c r="O410" t="n">
+        <v>-5.317752117100257</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -24519,6 +26983,12 @@
       <c r="M411" t="n">
         <v>0.1495828493426096</v>
       </c>
+      <c r="N411" t="n">
+        <v>10.34879808092298</v>
+      </c>
+      <c r="O411" t="n">
+        <v>-9.731853076067502</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -24562,6 +27032,12 @@
       <c r="M412" t="n">
         <v>0</v>
       </c>
+      <c r="N412" t="n">
+        <v>11.03572292929995</v>
+      </c>
+      <c r="O412" t="n">
+        <v>-10.37556475177415</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -24605,6 +27081,12 @@
       <c r="M413" t="n">
         <v>0</v>
       </c>
+      <c r="N413" t="n">
+        <v>13.74785471901889</v>
+      </c>
+      <c r="O413" t="n">
+        <v>-12.969065605354</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -24648,6 +27130,12 @@
       <c r="M414" t="n">
         <v>0</v>
       </c>
+      <c r="N414" t="n">
+        <v>13.9944121544479</v>
+      </c>
+      <c r="O414" t="n">
+        <v>-13.20483841022491</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -24691,6 +27179,12 @@
       <c r="M415" t="n">
         <v>0</v>
       </c>
+      <c r="N415" t="n">
+        <v>4.546697587757213</v>
+      </c>
+      <c r="O415" t="n">
+        <v>-4.308923813502775</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -24734,6 +27228,12 @@
       <c r="M416" t="n">
         <v>0</v>
       </c>
+      <c r="N416" t="n">
+        <v>6.932878153576391</v>
+      </c>
+      <c r="O416" t="n">
+        <v>-6.522813268208571</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -24777,6 +27277,12 @@
       <c r="M417" t="n">
         <v>0.09579606633239952</v>
       </c>
+      <c r="N417" t="n">
+        <v>10.36445318120625</v>
+      </c>
+      <c r="O417" t="n">
+        <v>-9.742089018376038</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -24820,6 +27326,12 @@
       <c r="M418" t="n">
         <v>0</v>
       </c>
+      <c r="N418" t="n">
+        <v>22.55184524079763</v>
+      </c>
+      <c r="O418" t="n">
+        <v>-21.3606319490971</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -24863,6 +27375,12 @@
       <c r="M419" t="n">
         <v>0</v>
       </c>
+      <c r="N419" t="n">
+        <v>2.679650149181636</v>
+      </c>
+      <c r="O419" t="n">
+        <v>-2.600696501492973</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -24906,6 +27424,12 @@
       <c r="M420" t="n">
         <v>0</v>
       </c>
+      <c r="N420" t="n">
+        <v>3.828974338750564</v>
+      </c>
+      <c r="O420" t="n">
+        <v>-3.652253536345337</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -24949,6 +27473,12 @@
       <c r="M421" t="n">
         <v>0</v>
       </c>
+      <c r="N421" t="n">
+        <v>6.029034956839751</v>
+      </c>
+      <c r="O421" t="n">
+        <v>-5.670470970628989</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -24992,6 +27522,12 @@
       <c r="M422" t="n">
         <v>0.1849181206798227</v>
       </c>
+      <c r="N422" t="n">
+        <v>9.704181574706629</v>
+      </c>
+      <c r="O422" t="n">
+        <v>-9.180067975785022</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -25035,6 +27571,12 @@
       <c r="M423" t="n">
         <v>0</v>
       </c>
+      <c r="N423" t="n">
+        <v>11.26465977115203</v>
+      </c>
+      <c r="O423" t="n">
+        <v>-10.59448770275303</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -25078,6 +27620,12 @@
       <c r="M424" t="n">
         <v>0</v>
       </c>
+      <c r="N424" t="n">
+        <v>14.35383011255231</v>
+      </c>
+      <c r="O424" t="n">
+        <v>-13.54853512318588</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -25121,6 +27669,12 @@
       <c r="M425" t="n">
         <v>0</v>
       </c>
+      <c r="N425" t="n">
+        <v>19.10868790075982</v>
+      </c>
+      <c r="O425" t="n">
+        <v>-18.09541141405841</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -25164,6 +27718,12 @@
       <c r="M426" t="n">
         <v>0</v>
       </c>
+      <c r="N426" t="n">
+        <v>25.63816739220348</v>
+      </c>
+      <c r="O426" t="n">
+        <v>-24.26502286948896</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -25207,6 +27767,12 @@
       <c r="M427" t="n">
         <v>0</v>
       </c>
+      <c r="N427" t="n">
+        <v>6.432325303838369</v>
+      </c>
+      <c r="O427" t="n">
+        <v>-6.049267359693795</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -25250,6 +27816,12 @@
       <c r="M428" t="n">
         <v>0</v>
       </c>
+      <c r="N428" t="n">
+        <v>20.8736231827128</v>
+      </c>
+      <c r="O428" t="n">
+        <v>-19.78329692290454</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -25293,6 +27865,12 @@
       <c r="M429" t="n">
         <v>0</v>
       </c>
+      <c r="N429" t="n">
+        <v>18.95047518635778</v>
+      </c>
+      <c r="O429" t="n">
+        <v>-17.94426904489802</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -25336,6 +27914,12 @@
       <c r="M430" t="n">
         <v>0</v>
       </c>
+      <c r="N430" t="n">
+        <v>18.28477011069672</v>
+      </c>
+      <c r="O430" t="n">
+        <v>-17.30768247174195</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -25379,6 +27963,12 @@
       <c r="M431" t="n">
         <v>0</v>
       </c>
+      <c r="N431" t="n">
+        <v>20.79725931158756</v>
+      </c>
+      <c r="O431" t="n">
+        <v>-19.72190440067043</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -25422,6 +28012,12 @@
       <c r="M432" t="n">
         <v>0</v>
       </c>
+      <c r="N432" t="n">
+        <v>4.890847533806133</v>
+      </c>
+      <c r="O432" t="n">
+        <v>-4.624174169423201</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -25465,6 +28061,12 @@
       <c r="M433" t="n">
         <v>0</v>
       </c>
+      <c r="N433" t="n">
+        <v>7.856692482753376</v>
+      </c>
+      <c r="O433" t="n">
+        <v>-7.391714707174595</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -25508,6 +28110,12 @@
       <c r="M434" t="n">
         <v>0</v>
       </c>
+      <c r="N434" t="n">
+        <v>13.0252628244641</v>
+      </c>
+      <c r="O434" t="n">
+        <v>-12.38603851822372</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -25551,6 +28159,12 @@
       <c r="M435" t="n">
         <v>0</v>
       </c>
+      <c r="N435" t="n">
+        <v>16.97377458438021</v>
+      </c>
+      <c r="O435" t="n">
+        <v>-16.17105191701286</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -25594,6 +28208,12 @@
       <c r="M436" t="n">
         <v>0</v>
       </c>
+      <c r="N436" t="n">
+        <v>8.620357923947767</v>
+      </c>
+      <c r="O436" t="n">
+        <v>-8.124290507206709</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -25637,6 +28257,12 @@
       <c r="M437" t="n">
         <v>0</v>
       </c>
+      <c r="N437" t="n">
+        <v>9.71722994541277</v>
+      </c>
+      <c r="O437" t="n">
+        <v>-9.183765322139713</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -25680,6 +28306,12 @@
       <c r="M438" t="n">
         <v>0</v>
       </c>
+      <c r="N438" t="n">
+        <v>10.79295119255563</v>
+      </c>
+      <c r="O438" t="n">
+        <v>-10.2250951523231</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -25723,6 +28355,12 @@
       <c r="M439" t="n">
         <v>0</v>
       </c>
+      <c r="N439" t="n">
+        <v>12.43277016685876</v>
+      </c>
+      <c r="O439" t="n">
+        <v>-11.81248818613926</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -25766,6 +28404,12 @@
       <c r="M440" t="n">
         <v>0</v>
       </c>
+      <c r="N440" t="n">
+        <v>16.02391136679212</v>
+      </c>
+      <c r="O440" t="n">
+        <v>-15.2867481629775</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -25809,6 +28453,12 @@
       <c r="M441" t="n">
         <v>0</v>
       </c>
+      <c r="N441" t="n">
+        <v>16.43926741822666</v>
+      </c>
+      <c r="O441" t="n">
+        <v>-15.67465759772508</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -25852,6 +28502,12 @@
       <c r="M442" t="n">
         <v>0</v>
       </c>
+      <c r="N442" t="n">
+        <v>18.33885258977945</v>
+      </c>
+      <c r="O442" t="n">
+        <v>-17.43879351183765</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -25895,6 +28551,12 @@
       <c r="M443" t="n">
         <v>0</v>
       </c>
+      <c r="N443" t="n">
+        <v>18.80919260104604</v>
+      </c>
+      <c r="O443" t="n">
+        <v>-17.87559609281441</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -25938,6 +28600,12 @@
       <c r="M444" t="n">
         <v>0</v>
       </c>
+      <c r="N444" t="n">
+        <v>3.135533906065501</v>
+      </c>
+      <c r="O444" t="n">
+        <v>-3.01780046067064</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -25981,6 +28649,12 @@
       <c r="M445" t="n">
         <v>0</v>
       </c>
+      <c r="N445" t="n">
+        <v>3.818355042367932</v>
+      </c>
+      <c r="O445" t="n">
+        <v>-3.642537566879736</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -26024,6 +28698,12 @@
       <c r="M446" t="n">
         <v>0</v>
       </c>
+      <c r="N446" t="n">
+        <v>3.590747996933788</v>
+      </c>
+      <c r="O446" t="n">
+        <v>-3.434291864810037</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -26067,6 +28747,12 @@
       <c r="M447" t="n">
         <v>0</v>
       </c>
+      <c r="N447" t="n">
+        <v>4.95967987048103</v>
+      </c>
+      <c r="O447" t="n">
+        <v>-4.687226710121116</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -26110,6 +28796,12 @@
       <c r="M448" t="n">
         <v>0</v>
       </c>
+      <c r="N448" t="n">
+        <v>5.189120992730719</v>
+      </c>
+      <c r="O448" t="n">
+        <v>-4.897401845780831</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -26153,6 +28845,12 @@
       <c r="M449" t="n">
         <v>0</v>
       </c>
+      <c r="N449" t="n">
+        <v>5.648003237230095</v>
+      </c>
+      <c r="O449" t="n">
+        <v>-5.317752117100254</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -26196,6 +28894,12 @@
       <c r="M450" t="n">
         <v>0</v>
       </c>
+      <c r="N450" t="n">
+        <v>12.95095558670057</v>
+      </c>
+      <c r="O450" t="n">
+        <v>-12.31410692491877</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -26239,6 +28943,12 @@
       <c r="M451" t="n">
         <v>0</v>
       </c>
+      <c r="N451" t="n">
+        <v>14.43710034702207</v>
+      </c>
+      <c r="O451" t="n">
+        <v>-13.75273879633117</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -26282,6 +28992,12 @@
       <c r="M452" t="n">
         <v>0</v>
       </c>
+      <c r="N452" t="n">
+        <v>17.04702141762154</v>
+      </c>
+      <c r="O452" t="n">
+        <v>-16.23907591036221</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -26325,6 +29041,12 @@
       <c r="M453" t="n">
         <v>0</v>
       </c>
+      <c r="N453" t="n">
+        <v>17.19351508532276</v>
+      </c>
+      <c r="O453" t="n">
+        <v>-16.37512389823421</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -26368,6 +29090,12 @@
       <c r="M454" t="n">
         <v>0</v>
       </c>
+      <c r="N454" t="n">
+        <v>4.546697587757209</v>
+      </c>
+      <c r="O454" t="n">
+        <v>-4.308923813502778</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -26411,6 +29139,12 @@
       <c r="M455" t="n">
         <v>0</v>
       </c>
+      <c r="N455" t="n">
+        <v>6.834846271754432</v>
+      </c>
+      <c r="O455" t="n">
+        <v>-6.419684542041548</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -26454,6 +29188,12 @@
       <c r="M456" t="n">
         <v>0</v>
       </c>
+      <c r="N456" t="n">
+        <v>13.13672368174069</v>
+      </c>
+      <c r="O456" t="n">
+        <v>-12.49393590884524</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -26497,6 +29237,12 @@
       <c r="M457" t="n">
         <v>0</v>
       </c>
+      <c r="N457" t="n">
+        <v>22.65772888971364</v>
+      </c>
+      <c r="O457" t="n">
+        <v>-21.4497138450279</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -26540,6 +29286,12 @@
       <c r="M458" t="n">
         <v>0</v>
       </c>
+      <c r="N458" t="n">
+        <v>2.679650149181639</v>
+      </c>
+      <c r="O458" t="n">
+        <v>-2.600696501492973</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -26583,6 +29335,12 @@
       <c r="M459" t="n">
         <v>0</v>
       </c>
+      <c r="N459" t="n">
+        <v>3.828974330002097</v>
+      </c>
+      <c r="O459" t="n">
+        <v>-3.652253527142032</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -26626,6 +29384,12 @@
       <c r="M460" t="n">
         <v>0</v>
       </c>
+      <c r="N460" t="n">
+        <v>6.001953240837802</v>
+      </c>
+      <c r="O460" t="n">
+        <v>-5.641981230130372</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -26669,6 +29433,12 @@
       <c r="M461" t="n">
         <v>0</v>
       </c>
+      <c r="N461" t="n">
+        <v>9.774857869777502</v>
+      </c>
+      <c r="O461" t="n">
+        <v>-9.239550849188664</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -26712,6 +29482,12 @@
       <c r="M462" t="n">
         <v>0</v>
       </c>
+      <c r="N462" t="n">
+        <v>14.78208415124385</v>
+      </c>
+      <c r="O462" t="n">
+        <v>-14.08669327314775</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -26755,6 +29531,12 @@
       <c r="M463" t="n">
         <v>0</v>
       </c>
+      <c r="N463" t="n">
+        <v>17.40706554942465</v>
+      </c>
+      <c r="O463" t="n">
+        <v>-16.57344722103108</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -26798,6 +29580,12 @@
       <c r="M464" t="n">
         <v>0</v>
       </c>
+      <c r="N464" t="n">
+        <v>20.23219453221911</v>
+      </c>
+      <c r="O464" t="n">
+        <v>-19.19713136805706</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -26841,6 +29629,12 @@
       <c r="M465" t="n">
         <v>0</v>
       </c>
+      <c r="N465" t="n">
+        <v>26.13441431839587</v>
+      </c>
+      <c r="O465" t="n">
+        <v>-24.74321665566241</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -26884,6 +29678,12 @@
       <c r="M466" t="n">
         <v>0</v>
       </c>
+      <c r="N466" t="n">
+        <v>6.359971022651819</v>
+      </c>
+      <c r="O466" t="n">
+        <v>-5.9731512563117</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -26927,6 +29727,12 @@
       <c r="M467" t="n">
         <v>0</v>
       </c>
+      <c r="N467" t="n">
+        <v>21.28068841339296</v>
+      </c>
+      <c r="O467" t="n">
+        <v>-20.17086275909907</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -26970,6 +29776,12 @@
       <c r="M468" t="n">
         <v>0</v>
       </c>
+      <c r="N468" t="n">
+        <v>20.13803780538235</v>
+      </c>
+      <c r="O468" t="n">
+        <v>-19.10968845375399</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -27013,6 +29825,12 @@
       <c r="M469" t="n">
         <v>0</v>
       </c>
+      <c r="N469" t="n">
+        <v>19.74250490260892</v>
+      </c>
+      <c r="O469" t="n">
+        <v>-18.74235888651874</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -27056,6 +29874,12 @@
       <c r="M470" t="n">
         <v>0</v>
       </c>
+      <c r="N470" t="n">
+        <v>21.10314633682186</v>
+      </c>
+      <c r="O470" t="n">
+        <v>-20.0161520709718</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -27099,6 +29923,12 @@
       <c r="M471" t="n">
         <v>0</v>
       </c>
+      <c r="N471" t="n">
+        <v>4.890847533806122</v>
+      </c>
+      <c r="O471" t="n">
+        <v>-4.624174169423201</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -27142,6 +29972,12 @@
       <c r="M472" t="n">
         <v>0</v>
       </c>
+      <c r="N472" t="n">
+        <v>7.875712884448938</v>
+      </c>
+      <c r="O472" t="n">
+        <v>-7.411724011919063</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -27185,6 +30021,12 @@
       <c r="M473" t="n">
         <v>0</v>
       </c>
+      <c r="N473" t="n">
+        <v>12.91938301168945</v>
+      </c>
+      <c r="O473" t="n">
+        <v>-12.27465383381988</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -27228,6 +30070,12 @@
       <c r="M474" t="n">
         <v>0</v>
       </c>
+      <c r="N474" t="n">
+        <v>17.31332499104048</v>
+      </c>
+      <c r="O474" t="n">
+        <v>-16.49778778998116</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -27271,6 +30119,12 @@
       <c r="M475" t="n">
         <v>0</v>
       </c>
+      <c r="N475" t="n">
+        <v>8.602580854246312</v>
+      </c>
+      <c r="O475" t="n">
+        <v>-8.105589177402379</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -27314,6 +30168,12 @@
       <c r="M476" t="n">
         <v>0</v>
       </c>
+      <c r="N476" t="n">
+        <v>9.677072339818134</v>
+      </c>
+      <c r="O476" t="n">
+        <v>-9.141519854298826</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -27357,6 +30217,12 @@
       <c r="M477" t="n">
         <v>0</v>
       </c>
+      <c r="N477" t="n">
+        <v>10.73142165485769</v>
+      </c>
+      <c r="O477" t="n">
+        <v>-10.16036658926281</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -27400,6 +30266,12 @@
       <c r="M478" t="n">
         <v>0</v>
       </c>
+      <c r="N478" t="n">
+        <v>12.33866146436922</v>
+      </c>
+      <c r="O478" t="n">
+        <v>-11.71348661207378</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -27443,6 +30315,12 @@
       <c r="M479" t="n">
         <v>0</v>
       </c>
+      <c r="N479" t="n">
+        <v>15.92329328194646</v>
+      </c>
+      <c r="O479" t="n">
+        <v>-15.17741490537339</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -27486,6 +30364,12 @@
       <c r="M480" t="n">
         <v>0</v>
       </c>
+      <c r="N480" t="n">
+        <v>16.71678667550112</v>
+      </c>
+      <c r="O480" t="n">
+        <v>-15.94167400262381</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -27529,6 +30413,12 @@
       <c r="M481" t="n">
         <v>0</v>
       </c>
+      <c r="N481" t="n">
+        <v>18.66638434203108</v>
+      </c>
+      <c r="O481" t="n">
+        <v>-17.75393029809302</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -27572,6 +30462,12 @@
       <c r="M482" t="n">
         <v>0</v>
       </c>
+      <c r="N482" t="n">
+        <v>19.13258330492727</v>
+      </c>
+      <c r="O482" t="n">
+        <v>-18.1867363934818</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -27615,6 +30511,12 @@
       <c r="M483" t="n">
         <v>0</v>
       </c>
+      <c r="N483" t="n">
+        <v>3.135533906065503</v>
+      </c>
+      <c r="O483" t="n">
+        <v>-3.017800460670638</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -27658,6 +30560,12 @@
       <c r="M484" t="n">
         <v>0</v>
       </c>
+      <c r="N484" t="n">
+        <v>3.81835504236793</v>
+      </c>
+      <c r="O484" t="n">
+        <v>-3.642537566879735</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -27701,6 +30609,12 @@
       <c r="M485" t="n">
         <v>0</v>
       </c>
+      <c r="N485" t="n">
+        <v>3.590747996933787</v>
+      </c>
+      <c r="O485" t="n">
+        <v>-3.434291864810038</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -27744,6 +30658,12 @@
       <c r="M486" t="n">
         <v>0</v>
       </c>
+      <c r="N486" t="n">
+        <v>4.959679870481031</v>
+      </c>
+      <c r="O486" t="n">
+        <v>-4.687226710121113</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -27787,6 +30707,12 @@
       <c r="M487" t="n">
         <v>0</v>
       </c>
+      <c r="N487" t="n">
+        <v>5.18912099273072</v>
+      </c>
+      <c r="O487" t="n">
+        <v>-4.897401845780826</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -27830,6 +30756,12 @@
       <c r="M488" t="n">
         <v>0</v>
       </c>
+      <c r="N488" t="n">
+        <v>5.648003237230089</v>
+      </c>
+      <c r="O488" t="n">
+        <v>-5.317752117100252</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -27873,6 +30805,12 @@
       <c r="M489" t="n">
         <v>0</v>
       </c>
+      <c r="N489" t="n">
+        <v>12.84655207451621</v>
+      </c>
+      <c r="O489" t="n">
+        <v>-12.20427529648499</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -27916,6 +30854,12 @@
       <c r="M490" t="n">
         <v>0</v>
       </c>
+      <c r="N490" t="n">
+        <v>14.30317081798078</v>
+      </c>
+      <c r="O490" t="n">
+        <v>-13.61184604318319</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -27959,6 +30903,12 @@
       <c r="M491" t="n">
         <v>0</v>
       </c>
+      <c r="N491" t="n">
+        <v>17.38592693253046</v>
+      </c>
+      <c r="O491" t="n">
+        <v>-16.56518940455946</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -28002,6 +30952,12 @@
       <c r="M492" t="n">
         <v>0</v>
       </c>
+      <c r="N492" t="n">
+        <v>17.531130815511</v>
+      </c>
+      <c r="O492" t="n">
+        <v>-16.69999263371649</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -28045,6 +31001,12 @@
       <c r="M493" t="n">
         <v>0</v>
       </c>
+      <c r="N493" t="n">
+        <v>4.546697587757203</v>
+      </c>
+      <c r="O493" t="n">
+        <v>-4.308923813502774</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -28088,6 +31050,12 @@
       <c r="M494" t="n">
         <v>0</v>
       </c>
+      <c r="N494" t="n">
+        <v>6.859928741739745</v>
+      </c>
+      <c r="O494" t="n">
+        <v>-6.446071092321252</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -28131,6 +31099,12 @@
       <c r="M495" t="n">
         <v>0</v>
       </c>
+      <c r="N495" t="n">
+        <v>13.02862915622161</v>
+      </c>
+      <c r="O495" t="n">
+        <v>-12.38022136501291</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -28174,6 +31148,12 @@
       <c r="M496" t="n">
         <v>0</v>
       </c>
+      <c r="N496" t="n">
+        <v>22.94723564975869</v>
+      </c>
+      <c r="O496" t="n">
+        <v>-21.72815308038528</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -28217,6 +31197,12 @@
       <c r="M497" t="n">
         <v>0</v>
       </c>
+      <c r="N497" t="n">
+        <v>2.67964982729166</v>
+      </c>
+      <c r="O497" t="n">
+        <v>-2.600696060142714</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -28260,6 +31246,12 @@
       <c r="M498" t="n">
         <v>0</v>
       </c>
+      <c r="N498" t="n">
+        <v>3.828974316004577</v>
+      </c>
+      <c r="O498" t="n">
+        <v>-3.652253512416747</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -28303,6 +31295,12 @@
       <c r="M499" t="n">
         <v>0</v>
       </c>
+      <c r="N499" t="n">
+        <v>6.00195324083781</v>
+      </c>
+      <c r="O499" t="n">
+        <v>-5.641981230130368</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -28346,6 +31344,12 @@
       <c r="M500" t="n">
         <v>0</v>
       </c>
+      <c r="N500" t="n">
+        <v>9.748603490402076</v>
+      </c>
+      <c r="O500" t="n">
+        <v>-9.21193145995557</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -28389,6 +31393,12 @@
       <c r="M501" t="n">
         <v>0</v>
       </c>
+      <c r="N501" t="n">
+        <v>14.65633226032817</v>
+      </c>
+      <c r="O501" t="n">
+        <v>-13.95440332744638</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -28432,6 +31442,12 @@
       <c r="M502" t="n">
         <v>0</v>
       </c>
+      <c r="N502" t="n">
+        <v>17.7106674352925</v>
+      </c>
+      <c r="O502" t="n">
+        <v>-16.86555991641617</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -28475,6 +31491,12 @@
       <c r="M503" t="n">
         <v>0</v>
       </c>
+      <c r="N503" t="n">
+        <v>20.51096353885805</v>
+      </c>
+      <c r="O503" t="n">
+        <v>-19.46527800378189</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -28518,6 +31540,12 @@
       <c r="M504" t="n">
         <v>0</v>
       </c>
+      <c r="N504" t="n">
+        <v>25.6959388022196</v>
+      </c>
+      <c r="O504" t="n">
+        <v>-24.29668363944071</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -28561,6 +31589,12 @@
       <c r="M505" t="n">
         <v>0</v>
       </c>
+      <c r="N505" t="n">
+        <v>6.382156908715988</v>
+      </c>
+      <c r="O505" t="n">
+        <v>-5.996490624343407</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -28604,6 +31638,12 @@
       <c r="M506" t="n">
         <v>0</v>
       </c>
+      <c r="N506" t="n">
+        <v>21.5502411604975</v>
+      </c>
+      <c r="O506" t="n">
+        <v>-20.43011483919022</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -28647,6 +31687,12 @@
       <c r="M507" t="n">
         <v>0</v>
       </c>
+      <c r="N507" t="n">
+        <v>20.41763444949866</v>
+      </c>
+      <c r="O507" t="n">
+        <v>-19.37863383733966</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -28690,6 +31736,12 @@
       <c r="M508" t="n">
         <v>0</v>
       </c>
+      <c r="N508" t="n">
+        <v>20.02557828030675</v>
+      </c>
+      <c r="O508" t="n">
+        <v>-19.01465964439136</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -28733,6 +31785,12 @@
       <c r="M509" t="n">
         <v>0</v>
       </c>
+      <c r="N509" t="n">
+        <v>20.33690702844013</v>
+      </c>
+      <c r="O509" t="n">
+        <v>-19.27149337456649</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -28776,6 +31834,12 @@
       <c r="M510" t="n">
         <v>0</v>
       </c>
+      <c r="N510" t="n">
+        <v>4.890847504650439</v>
+      </c>
+      <c r="O510" t="n">
+        <v>-4.62417413875165</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -28819,6 +31883,12 @@
       <c r="M511" t="n">
         <v>0</v>
       </c>
+      <c r="N511" t="n">
+        <v>7.696491312663595</v>
+      </c>
+      <c r="O511" t="n">
+        <v>-7.2231844056567</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -28862,6 +31932,12 @@
       <c r="M512" t="n">
         <v>0</v>
       </c>
+      <c r="N512" t="n">
+        <v>12.9024563716372</v>
+      </c>
+      <c r="O512" t="n">
+        <v>-12.25684714894929</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -28905,6 +31981,12 @@
       <c r="M513" t="n">
         <v>0</v>
       </c>
+      <c r="N513" t="n">
+        <v>16.95689231671998</v>
+      </c>
+      <c r="O513" t="n">
+        <v>-16.15218880358717</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -28948,6 +32030,12 @@
       <c r="M514" t="n">
         <v>0</v>
       </c>
+      <c r="N514" t="n">
+        <v>8.46575643620851</v>
+      </c>
+      <c r="O514" t="n">
+        <v>-7.961651025053048</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -28991,6 +32079,12 @@
       <c r="M515" t="n">
         <v>0</v>
       </c>
+      <c r="N515" t="n">
+        <v>9.570875868790267</v>
+      </c>
+      <c r="O515" t="n">
+        <v>-9.029802048040359</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -29034,6 +32128,12 @@
       <c r="M516" t="n">
         <v>0</v>
       </c>
+      <c r="N516" t="n">
+        <v>10.65404432589851</v>
+      </c>
+      <c r="O516" t="n">
+        <v>-10.07896628130732</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -29077,6 +32177,12 @@
       <c r="M517" t="n">
         <v>0</v>
       </c>
+      <c r="N517" t="n">
+        <v>12.30569039625567</v>
+      </c>
+      <c r="O517" t="n">
+        <v>-11.67880132202608</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -29120,6 +32226,12 @@
       <c r="M518" t="n">
         <v>0</v>
       </c>
+      <c r="N518" t="n">
+        <v>15.91525010400267</v>
+      </c>
+      <c r="O518" t="n">
+        <v>-15.17312701176728</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -29163,6 +32275,12 @@
       <c r="M519" t="n">
         <v>0</v>
       </c>
+      <c r="N519" t="n">
+        <v>16.48438040283139</v>
+      </c>
+      <c r="O519" t="n">
+        <v>-15.71612307648778</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -29206,6 +32324,12 @@
       <c r="M520" t="n">
         <v>0</v>
       </c>
+      <c r="N520" t="n">
+        <v>18.16364062849612</v>
+      </c>
+      <c r="O520" t="n">
+        <v>-17.26585718847557</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -29249,6 +32373,12 @@
       <c r="M521" t="n">
         <v>0</v>
       </c>
+      <c r="N521" t="n">
+        <v>18.57942786735559</v>
+      </c>
+      <c r="O521" t="n">
+        <v>-17.64957357593106</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -29292,6 +32422,12 @@
       <c r="M522" t="n">
         <v>0</v>
       </c>
+      <c r="N522" t="n">
+        <v>3.13553389674018</v>
+      </c>
+      <c r="O522" t="n">
+        <v>-3.017800450860483</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -29335,6 +32471,12 @@
       <c r="M523" t="n">
         <v>0</v>
       </c>
+      <c r="N523" t="n">
+        <v>3.818355028442009</v>
+      </c>
+      <c r="O523" t="n">
+        <v>-3.64253755222972</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -29378,6 +32520,12 @@
       <c r="M524" t="n">
         <v>0</v>
       </c>
+      <c r="N524" t="n">
+        <v>3.590747988671693</v>
+      </c>
+      <c r="O524" t="n">
+        <v>-3.434291856118356</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -29421,6 +32569,12 @@
       <c r="M525" t="n">
         <v>0</v>
       </c>
+      <c r="N525" t="n">
+        <v>4.95967990771554</v>
+      </c>
+      <c r="O525" t="n">
+        <v>-4.687226749291511</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -29464,6 +32618,12 @@
       <c r="M526" t="n">
         <v>0</v>
       </c>
+      <c r="N526" t="n">
+        <v>5.189121032598194</v>
+      </c>
+      <c r="O526" t="n">
+        <v>-4.897401887721082</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -29507,6 +32667,12 @@
       <c r="M527" t="n">
         <v>0</v>
       </c>
+      <c r="N527" t="n">
+        <v>5.648003282363491</v>
+      </c>
+      <c r="O527" t="n">
+        <v>-5.31775216458022</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -29550,6 +32716,12 @@
       <c r="M528" t="n">
         <v>0</v>
       </c>
+      <c r="N528" t="n">
+        <v>12.83696359103139</v>
+      </c>
+      <c r="O528" t="n">
+        <v>-12.1941882914282</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -29593,6 +32765,12 @@
       <c r="M529" t="n">
         <v>0</v>
       </c>
+      <c r="N529" t="n">
+        <v>14.3338211677942</v>
+      </c>
+      <c r="O529" t="n">
+        <v>-13.64408995683745</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -29636,6 +32814,12 @@
       <c r="M530" t="n">
         <v>0</v>
       </c>
+      <c r="N530" t="n">
+        <v>17.0027805130198</v>
+      </c>
+      <c r="O530" t="n">
+        <v>-16.19377035366636</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -29679,6 +32863,12 @@
       <c r="M531" t="n">
         <v>0</v>
       </c>
+      <c r="N531" t="n">
+        <v>17.13228447447369</v>
+      </c>
+      <c r="O531" t="n">
+        <v>-16.31328536679815</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -29722,6 +32912,12 @@
       <c r="M532" t="n">
         <v>0</v>
       </c>
+      <c r="N532" t="n">
+        <v>4.546697611298912</v>
+      </c>
+      <c r="O532" t="n">
+        <v>-4.308923838268441</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -29765,6 +32961,12 @@
       <c r="M533" t="n">
         <v>0</v>
       </c>
+      <c r="N533" t="n">
+        <v>6.761145018242834</v>
+      </c>
+      <c r="O533" t="n">
+        <v>-6.342151434951293</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -29808,6 +33010,12 @@
       <c r="M534" t="n">
         <v>0</v>
       </c>
+      <c r="N534" t="n">
+        <v>13.02407040456614</v>
+      </c>
+      <c r="O534" t="n">
+        <v>-12.3754255961018</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -29851,6 +33059,12 @@
       <c r="M535" t="n">
         <v>0</v>
       </c>
+      <c r="N535" t="n">
+        <v>21.96278223670048</v>
+      </c>
+      <c r="O535" t="n">
+        <v>-20.77119535661153</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -29894,6 +33108,12 @@
       <c r="M536" t="n">
         <v>0</v>
       </c>
+      <c r="N536" t="n">
+        <v>2.679650149181635</v>
+      </c>
+      <c r="O536" t="n">
+        <v>-2.600696501492974</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -29937,6 +33157,12 @@
       <c r="M537" t="n">
         <v>0</v>
       </c>
+      <c r="N537" t="n">
+        <v>3.828974316004573</v>
+      </c>
+      <c r="O537" t="n">
+        <v>-3.652253512416747</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -29980,6 +33206,12 @@
       <c r="M538" t="n">
         <v>0</v>
       </c>
+      <c r="N538" t="n">
+        <v>6.001953240837808</v>
+      </c>
+      <c r="O538" t="n">
+        <v>-5.641981230130374</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -30023,6 +33255,12 @@
       <c r="M539" t="n">
         <v>0</v>
       </c>
+      <c r="N539" t="n">
+        <v>9.638248045380958</v>
+      </c>
+      <c r="O539" t="n">
+        <v>-9.095838447569159</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -30066,6 +33304,12 @@
       <c r="M540" t="n">
         <v>0</v>
       </c>
+      <c r="N540" t="n">
+        <v>14.68177058735618</v>
+      </c>
+      <c r="O540" t="n">
+        <v>-13.98116423638196</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -30109,6 +33353,12 @@
       <c r="M541" t="n">
         <v>0</v>
       </c>
+      <c r="N541" t="n">
+        <v>17.3210682736819</v>
+      </c>
+      <c r="O541" t="n">
+        <v>-16.48750782291566</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -30152,6 +33402,12 @@
       <c r="M542" t="n">
         <v>0</v>
       </c>
+      <c r="N542" t="n">
+        <v>19.81855093385265</v>
+      </c>
+      <c r="O542" t="n">
+        <v>-18.79235371006671</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -30195,6 +33451,12 @@
       <c r="M543" t="n">
         <v>0</v>
       </c>
+      <c r="N543" t="n">
+        <v>24.25500235443277</v>
+      </c>
+      <c r="O543" t="n">
+        <v>-22.88661108904305</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -30238,6 +33500,12 @@
       <c r="M544" t="n">
         <v>0</v>
       </c>
+      <c r="N544" t="n">
+        <v>6.336326657011486</v>
+      </c>
+      <c r="O544" t="n">
+        <v>-5.948277579868936</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -30281,6 +33549,12 @@
       <c r="M545" t="n">
         <v>0</v>
       </c>
+      <c r="N545" t="n">
+        <v>20.73118435397912</v>
+      </c>
+      <c r="O545" t="n">
+        <v>-19.63401357233156</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -30324,6 +33598,12 @@
       <c r="M546" t="n">
         <v>0</v>
       </c>
+      <c r="N546" t="n">
+        <v>19.7210534546406</v>
+      </c>
+      <c r="O546" t="n">
+        <v>-18.70179646990508</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -30367,6 +33647,12 @@
       <c r="M547" t="n">
         <v>0</v>
       </c>
+      <c r="N547" t="n">
+        <v>19.37139275871445</v>
+      </c>
+      <c r="O547" t="n">
+        <v>-18.37910593444877</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -30410,6 +33696,12 @@
       <c r="M548" t="n">
         <v>0</v>
       </c>
+      <c r="N548" t="n">
+        <v>19.58753818297806</v>
+      </c>
+      <c r="O548" t="n">
+        <v>-18.52909377149986</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -30453,6 +33745,12 @@
       <c r="M549" t="n">
         <v>0</v>
       </c>
+      <c r="N549" t="n">
+        <v>4.906324154972918</v>
+      </c>
+      <c r="O549" t="n">
+        <v>-4.640455446459181</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -30496,6 +33794,12 @@
       <c r="M550" t="n">
         <v>0.9565996614977738</v>
       </c>
+      <c r="N550" t="n">
+        <v>8.369829633941977</v>
+      </c>
+      <c r="O550" t="n">
+        <v>-7.931530731997646</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -30539,6 +33843,12 @@
       <c r="M551" t="n">
         <v>0.04908416395525109</v>
       </c>
+      <c r="N551" t="n">
+        <v>9.953461601829526</v>
+      </c>
+      <c r="O551" t="n">
+        <v>-9.346790941466415</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -30582,6 +33892,12 @@
       <c r="M552" t="n">
         <v>0</v>
       </c>
+      <c r="N552" t="n">
+        <v>13.30010349584944</v>
+      </c>
+      <c r="O552" t="n">
+        <v>-12.53351455714493</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -30625,6 +33941,12 @@
       <c r="M553" t="n">
         <v>0.981353844387913</v>
       </c>
+      <c r="N553" t="n">
+        <v>8.957504315811583</v>
+      </c>
+      <c r="O553" t="n">
+        <v>-8.490128414846593</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -30668,6 +33990,12 @@
       <c r="M554" t="n">
         <v>0.7710912972179311</v>
       </c>
+      <c r="N554" t="n">
+        <v>9.261946791882607</v>
+      </c>
+      <c r="O554" t="n">
+        <v>-8.758893617509399</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -30711,6 +34039,12 @@
       <c r="M555" t="n">
         <v>0.5222903268200183</v>
       </c>
+      <c r="N555" t="n">
+        <v>9.458774627142496</v>
+      </c>
+      <c r="O555" t="n">
+        <v>-8.922021729933956</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -30754,6 +34088,12 @@
       <c r="M556" t="n">
         <v>0.1746811149970507</v>
       </c>
+      <c r="N556" t="n">
+        <v>9.822163743475484</v>
+      </c>
+      <c r="O556" t="n">
+        <v>-9.23405041101417</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -30797,6 +34137,12 @@
       <c r="M557" t="n">
         <v>0</v>
       </c>
+      <c r="N557" t="n">
+        <v>11.84209360660452</v>
+      </c>
+      <c r="O557" t="n">
+        <v>-11.14302246984381</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -30840,6 +34186,12 @@
       <c r="M558" t="n">
         <v>0</v>
       </c>
+      <c r="N558" t="n">
+        <v>12.42094389626772</v>
+      </c>
+      <c r="O558" t="n">
+        <v>-11.6950672409162</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -30883,6 +34235,12 @@
       <c r="M559" t="n">
         <v>0</v>
       </c>
+      <c r="N559" t="n">
+        <v>15.54538929698399</v>
+      </c>
+      <c r="O559" t="n">
+        <v>-14.67482517965824</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -30926,6 +34284,12 @@
       <c r="M560" t="n">
         <v>0</v>
       </c>
+      <c r="N560" t="n">
+        <v>16.31900645665727</v>
+      </c>
+      <c r="O560" t="n">
+        <v>-15.41261751635753</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -30969,6 +34333,12 @@
       <c r="M561" t="n">
         <v>0</v>
       </c>
+      <c r="N561" t="n">
+        <v>3.135533917722143</v>
+      </c>
+      <c r="O561" t="n">
+        <v>-3.017800472933331</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -31012,6 +34382,12 @@
       <c r="M562" t="n">
         <v>0</v>
       </c>
+      <c r="N562" t="n">
+        <v>3.818355059775396</v>
+      </c>
+      <c r="O562" t="n">
+        <v>-3.642537585192254</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -31055,6 +34431,12 @@
       <c r="M563" t="n">
         <v>0</v>
       </c>
+      <c r="N563" t="n">
+        <v>3.590748003130003</v>
+      </c>
+      <c r="O563" t="n">
+        <v>-3.434291871328402</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -31098,6 +34480,12 @@
       <c r="M564" t="n">
         <v>0</v>
       </c>
+      <c r="N564" t="n">
+        <v>4.990570116683938</v>
+      </c>
+      <c r="O564" t="n">
+        <v>-4.719722992786369</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -31141,6 +34529,12 @@
       <c r="M565" t="n">
         <v>0.1072211179024753</v>
       </c>
+      <c r="N565" t="n">
+        <v>5.268677642497356</v>
+      </c>
+      <c r="O565" t="n">
+        <v>-4.981094781140877</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -31184,6 +34578,12 @@
       <c r="M566" t="n">
         <v>0.8331924655822618</v>
       </c>
+      <c r="N566" t="n">
+        <v>5.846733467500111</v>
+      </c>
+      <c r="O566" t="n">
+        <v>-5.526814670197459</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -31227,6 +34627,12 @@
       <c r="M567" t="n">
         <v>0.06483604618691619</v>
       </c>
+      <c r="N567" t="n">
+        <v>9.936995282505507</v>
+      </c>
+      <c r="O567" t="n">
+        <v>-9.332651970433947</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -31270,6 +34676,12 @@
       <c r="M568" t="n">
         <v>0</v>
       </c>
+      <c r="N568" t="n">
+        <v>10.77009297036356</v>
+      </c>
+      <c r="O568" t="n">
+        <v>-10.12066426014578</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -31313,6 +34725,12 @@
       <c r="M569" t="n">
         <v>0</v>
       </c>
+      <c r="N569" t="n">
+        <v>13.4205801423966</v>
+      </c>
+      <c r="O569" t="n">
+        <v>-12.64841212560339</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -31356,6 +34774,12 @@
       <c r="M570" t="n">
         <v>0</v>
       </c>
+      <c r="N570" t="n">
+        <v>13.66153352167234</v>
+      </c>
+      <c r="O570" t="n">
+        <v>-12.87820738609954</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -31399,6 +34823,12 @@
       <c r="M571" t="n">
         <v>0</v>
       </c>
+      <c r="N571" t="n">
+        <v>4.547280013146596</v>
+      </c>
+      <c r="O571" t="n">
+        <v>-4.309536520179204</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -31442,6 +34872,12 @@
       <c r="M572" t="n">
         <v>1.035109407031019</v>
       </c>
+      <c r="N572" t="n">
+        <v>7.276232881253888</v>
+      </c>
+      <c r="O572" t="n">
+        <v>-6.884019592423732</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -31485,6 +34921,12 @@
       <c r="M573" t="n">
         <v>0.02545688110294417</v>
       </c>
+      <c r="N573" t="n">
+        <v>9.978162083904083</v>
+      </c>
+      <c r="O573" t="n">
+        <v>-9.368000367298681</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -31528,6 +34970,12 @@
       <c r="M574" t="n">
         <v>0</v>
       </c>
+      <c r="N574" t="n">
+        <v>22.64909456877216</v>
+      </c>
+      <c r="O574" t="n">
+        <v>-21.44957060277077</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -31571,6 +35019,12 @@
       <c r="M575" t="n">
         <v>0</v>
       </c>
+      <c r="N575" t="n">
+        <v>2.679649833545353</v>
+      </c>
+      <c r="O575" t="n">
+        <v>-2.600696066721549</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -31614,6 +35068,12 @@
       <c r="M576" t="n">
         <v>0</v>
       </c>
+      <c r="N576" t="n">
+        <v>3.828974330002104</v>
+      </c>
+      <c r="O576" t="n">
+        <v>-3.652253527142032</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -31657,6 +35117,12 @@
       <c r="M577" t="n">
         <v>1.198026070438548</v>
       </c>
+      <c r="N577" t="n">
+        <v>6.301246515577475</v>
+      </c>
+      <c r="O577" t="n">
+        <v>-5.956835271495334</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -31700,6 +35166,12 @@
       <c r="M578" t="n">
         <v>0.7566949679690468</v>
       </c>
+      <c r="N578" t="n">
+        <v>9.270354865695356</v>
+      </c>
+      <c r="O578" t="n">
+        <v>-8.765495974605512</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -31743,6 +35215,12 @@
       <c r="M579" t="n">
         <v>0</v>
       </c>
+      <c r="N579" t="n">
+        <v>10.99382625827239</v>
+      </c>
+      <c r="O579" t="n">
+        <v>-10.33403686084777</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -31786,6 +35264,12 @@
       <c r="M580" t="n">
         <v>0</v>
       </c>
+      <c r="N580" t="n">
+        <v>14.01278219291773</v>
+      </c>
+      <c r="O580" t="n">
+        <v>-13.21319036147535</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -31829,6 +35313,12 @@
       <c r="M581" t="n">
         <v>0</v>
       </c>
+      <c r="N581" t="n">
+        <v>18.65956581171846</v>
+      </c>
+      <c r="O581" t="n">
+        <v>-17.64478976615516</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -31872,6 +35362,12 @@
       <c r="M582" t="n">
         <v>0</v>
       </c>
+      <c r="N582" t="n">
+        <v>25.38506997507618</v>
+      </c>
+      <c r="O582" t="n">
+        <v>-23.99769537856388</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -31915,6 +35411,12 @@
       <c r="M583" t="n">
         <v>1.197163039799916</v>
       </c>
+      <c r="N583" t="n">
+        <v>6.746028964980612</v>
+      </c>
+      <c r="O583" t="n">
+        <v>-6.379281007970829</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -31958,6 +35460,12 @@
       <c r="M584" t="n">
         <v>0</v>
       </c>
+      <c r="N584" t="n">
+        <v>20.38501006962971</v>
+      </c>
+      <c r="O584" t="n">
+        <v>-19.29075310422186</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -32001,6 +35509,12 @@
       <c r="M585" t="n">
         <v>0</v>
       </c>
+      <c r="N585" t="n">
+        <v>18.5055737063784</v>
+      </c>
+      <c r="O585" t="n">
+        <v>-17.4983500653248</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -32044,6 +35558,12 @@
       <c r="M586" t="n">
         <v>0</v>
       </c>
+      <c r="N586" t="n">
+        <v>17.85499958063758</v>
+      </c>
+      <c r="O586" t="n">
+        <v>-16.87790285955273</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -32087,6 +35607,12 @@
       <c r="M587" t="n">
         <v>0</v>
       </c>
+      <c r="N587" t="n">
+        <v>19.26425925752044</v>
+      </c>
+      <c r="O587" t="n">
+        <v>-18.19834695756634</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -32130,6 +35656,12 @@
       <c r="M588" t="n">
         <v>0</v>
       </c>
+      <c r="N588" t="n">
+        <v>4.890847570250733</v>
+      </c>
+      <c r="O588" t="n">
+        <v>-4.62417420776264</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -32173,6 +35705,12 @@
       <c r="M589" t="n">
         <v>0</v>
       </c>
+      <c r="N589" t="n">
+        <v>7.911872773998715</v>
+      </c>
+      <c r="O589" t="n">
+        <v>-7.44976391565548</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -32216,6 +35754,12 @@
       <c r="M590" t="n">
         <v>0</v>
       </c>
+      <c r="N590" t="n">
+        <v>10.33685199088172</v>
+      </c>
+      <c r="O590" t="n">
+        <v>-9.71046333709552</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -32259,6 +35803,12 @@
       <c r="M591" t="n">
         <v>0</v>
       </c>
+      <c r="N591" t="n">
+        <v>13.31337832931049</v>
+      </c>
+      <c r="O591" t="n">
+        <v>-12.53135136892332</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -32302,6 +35852,12 @@
       <c r="M592" t="n">
         <v>0</v>
       </c>
+      <c r="N592" t="n">
+        <v>8.690253280831021</v>
+      </c>
+      <c r="O592" t="n">
+        <v>-8.197819842626918</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -32345,6 +35901,12 @@
       <c r="M593" t="n">
         <v>0</v>
       </c>
+      <c r="N593" t="n">
+        <v>9.368015067643018</v>
+      </c>
+      <c r="O593" t="n">
+        <v>-8.838842332010509</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -32388,6 +35950,12 @@
       <c r="M594" t="n">
         <v>0</v>
       </c>
+      <c r="N594" t="n">
+        <v>9.683065885288849</v>
+      </c>
+      <c r="O594" t="n">
+        <v>-9.122280033178358</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -32431,6 +35999,12 @@
       <c r="M595" t="n">
         <v>0</v>
       </c>
+      <c r="N595" t="n">
+        <v>10.16332627804164</v>
+      </c>
+      <c r="O595" t="n">
+        <v>-9.554349699592766</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -32474,6 +36048,12 @@
       <c r="M596" t="n">
         <v>0</v>
       </c>
+      <c r="N596" t="n">
+        <v>11.93373066979154</v>
+      </c>
+      <c r="O596" t="n">
+        <v>-11.21751946828617</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -32517,6 +36097,12 @@
       <c r="M597" t="n">
         <v>0</v>
       </c>
+      <c r="N597" t="n">
+        <v>12.48147007597731</v>
+      </c>
+      <c r="O597" t="n">
+        <v>-11.73912909819257</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -32560,6 +36146,12 @@
       <c r="M598" t="n">
         <v>0</v>
       </c>
+      <c r="N598" t="n">
+        <v>15.4379890568079</v>
+      </c>
+      <c r="O598" t="n">
+        <v>-14.55460805403622</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -32603,6 +36195,12 @@
       <c r="M599" t="n">
         <v>0</v>
       </c>
+      <c r="N599" t="n">
+        <v>16.17002739421849</v>
+      </c>
+      <c r="O599" t="n">
+        <v>-15.25172467909887</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -32646,6 +36244,12 @@
       <c r="M600" t="n">
         <v>0</v>
       </c>
+      <c r="N600" t="n">
+        <v>3.135533902688519</v>
+      </c>
+      <c r="O600" t="n">
+        <v>-3.017800457118083</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -32689,6 +36293,12 @@
       <c r="M601" t="n">
         <v>0</v>
       </c>
+      <c r="N601" t="n">
+        <v>3.818355037324916</v>
+      </c>
+      <c r="O601" t="n">
+        <v>-3.642537561574522</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -32732,6 +36342,12 @@
       <c r="M602" t="n">
         <v>0</v>
       </c>
+      <c r="N602" t="n">
+        <v>3.590747992446123</v>
+      </c>
+      <c r="O602" t="n">
+        <v>-3.434291860089042</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -32775,6 +36391,12 @@
       <c r="M603" t="n">
         <v>0</v>
       </c>
+      <c r="N603" t="n">
+        <v>4.959679859694027</v>
+      </c>
+      <c r="O603" t="n">
+        <v>-4.687226698773284</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -32818,6 +36440,12 @@
       <c r="M604" t="n">
         <v>0</v>
       </c>
+      <c r="N604" t="n">
+        <v>5.189120981180935</v>
+      </c>
+      <c r="O604" t="n">
+        <v>-4.897401833630557</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -32861,6 +36489,12 @@
       <c r="M605" t="n">
         <v>0</v>
       </c>
+      <c r="N605" t="n">
+        <v>5.648003224154762</v>
+      </c>
+      <c r="O605" t="n">
+        <v>-5.317752103345103</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -32904,6 +36538,12 @@
       <c r="M606" t="n">
         <v>0</v>
       </c>
+      <c r="N606" t="n">
+        <v>10.31508933056814</v>
+      </c>
+      <c r="O606" t="n">
+        <v>-9.690884405491177</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -32947,6 +36587,12 @@
       <c r="M607" t="n">
         <v>0</v>
       </c>
+      <c r="N607" t="n">
+        <v>10.91934577198466</v>
+      </c>
+      <c r="O607" t="n">
+        <v>-10.25152555740027</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -32990,6 +36636,12 @@
       <c r="M608" t="n">
         <v>0</v>
       </c>
+      <c r="N608" t="n">
+        <v>13.42737987965933</v>
+      </c>
+      <c r="O608" t="n">
+        <v>-12.63991450280537</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -33033,6 +36685,12 @@
       <c r="M609" t="n">
         <v>0</v>
       </c>
+      <c r="N609" t="n">
+        <v>13.65538298035702</v>
+      </c>
+      <c r="O609" t="n">
+        <v>-12.85704077056947</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -33076,6 +36734,12 @@
       <c r="M610" t="n">
         <v>0</v>
       </c>
+      <c r="N610" t="n">
+        <v>4.546697580937078</v>
+      </c>
+      <c r="O610" t="n">
+        <v>-4.308923806328055</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -33119,6 +36783,12 @@
       <c r="M611" t="n">
         <v>0</v>
       </c>
+      <c r="N611" t="n">
+        <v>6.862442341925046</v>
+      </c>
+      <c r="O611" t="n">
+        <v>-6.448715378857287</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -33162,6 +36832,12 @@
       <c r="M612" t="n">
         <v>0</v>
       </c>
+      <c r="N612" t="n">
+        <v>10.36949598135213</v>
+      </c>
+      <c r="O612" t="n">
+        <v>-9.739831734502042</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -33205,6 +36881,12 @@
       <c r="M613" t="n">
         <v>0</v>
       </c>
+      <c r="N613" t="n">
+        <v>22.1584208742125</v>
+      </c>
+      <c r="O613" t="n">
+        <v>-20.95494678144707</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -33248,6 +36930,12 @@
       <c r="M614" t="n">
         <v>0</v>
       </c>
+      <c r="N614" t="n">
+        <v>2.679650138921664</v>
+      </c>
+      <c r="O614" t="n">
+        <v>-2.600696490699564</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -33291,6 +36979,12 @@
       <c r="M615" t="n">
         <v>0</v>
       </c>
+      <c r="N615" t="n">
+        <v>3.828974324933133</v>
+      </c>
+      <c r="O615" t="n">
+        <v>-3.65225352180956</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -33334,6 +37028,12 @@
       <c r="M616" t="n">
         <v>0</v>
       </c>
+      <c r="N616" t="n">
+        <v>6.007811059754479</v>
+      </c>
+      <c r="O616" t="n">
+        <v>-5.648143607020068</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -33377,6 +37077,12 @@
       <c r="M617" t="n">
         <v>0</v>
       </c>
+      <c r="N617" t="n">
+        <v>9.372288168364932</v>
+      </c>
+      <c r="O617" t="n">
+        <v>-8.841996311172146</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -33420,6 +37126,12 @@
       <c r="M618" t="n">
         <v>0</v>
       </c>
+      <c r="N618" t="n">
+        <v>11.1299418932213</v>
+      </c>
+      <c r="O618" t="n">
+        <v>-10.4524542475125</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -33463,6 +37175,12 @@
       <c r="M619" t="n">
         <v>0</v>
       </c>
+      <c r="N619" t="n">
+        <v>13.98664333790388</v>
+      </c>
+      <c r="O619" t="n">
+        <v>-13.17287665715719</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -33506,6 +37224,12 @@
       <c r="M620" t="n">
         <v>0</v>
       </c>
+      <c r="N620" t="n">
+        <v>18.38368448866009</v>
+      </c>
+      <c r="O620" t="n">
+        <v>-17.36015681725674</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -33549,6 +37273,12 @@
       <c r="M621" t="n">
         <v>0</v>
       </c>
+      <c r="N621" t="n">
+        <v>26.19445321619542</v>
+      </c>
+      <c r="O621" t="n">
+        <v>-24.79831256940606</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -33592,6 +37322,12 @@
       <c r="M622" t="n">
         <v>0</v>
       </c>
+      <c r="N622" t="n">
+        <v>6.394449619259677</v>
+      </c>
+      <c r="O622" t="n">
+        <v>-6.009422453825339</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -33635,6 +37371,12 @@
       <c r="M623" t="n">
         <v>0</v>
       </c>
+      <c r="N623" t="n">
+        <v>20.01556422580289</v>
+      </c>
+      <c r="O623" t="n">
+        <v>-18.91418767863076</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -33678,6 +37420,12 @@
       <c r="M624" t="n">
         <v>0</v>
       </c>
+      <c r="N624" t="n">
+        <v>18.23713861233208</v>
+      </c>
+      <c r="O624" t="n">
+        <v>-17.22060191671019</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -33721,6 +37469,12 @@
       <c r="M625" t="n">
         <v>0</v>
       </c>
+      <c r="N625" t="n">
+        <v>17.62152974613062</v>
+      </c>
+      <c r="O625" t="n">
+        <v>-16.63436069142999</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -33764,6 +37518,12 @@
       <c r="M626" t="n">
         <v>0</v>
       </c>
+      <c r="N626" t="n">
+        <v>19.26970319850085</v>
+      </c>
+      <c r="O626" t="n">
+        <v>-18.20167638854359</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -33807,6 +37567,12 @@
       <c r="M627" t="n">
         <v>0</v>
       </c>
+      <c r="N627" t="n">
+        <v>4.890847533806119</v>
+      </c>
+      <c r="O627" t="n">
+        <v>-4.624174169423201</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -33850,6 +37616,12 @@
       <c r="M628" t="n">
         <v>0</v>
       </c>
+      <c r="N628" t="n">
+        <v>8.024987339566717</v>
+      </c>
+      <c r="O628" t="n">
+        <v>-7.568759499960898</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -33893,6 +37665,12 @@
       <c r="M629" t="n">
         <v>0</v>
       </c>
+      <c r="N629" t="n">
+        <v>10.24783695863758</v>
+      </c>
+      <c r="O629" t="n">
+        <v>-9.625398022021042</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -33936,6 +37714,12 @@
       <c r="M630" t="n">
         <v>0</v>
       </c>
+      <c r="N630" t="n">
+        <v>13.30925343191605</v>
+      </c>
+      <c r="O630" t="n">
+        <v>-12.52882864481362</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -33979,6 +37763,12 @@
       <c r="M631" t="n">
         <v>0</v>
       </c>
+      <c r="N631" t="n">
+        <v>8.805526434173622</v>
+      </c>
+      <c r="O631" t="n">
+        <v>-8.319086243358335</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -34022,6 +37812,12 @@
       <c r="M632" t="n">
         <v>0</v>
       </c>
+      <c r="N632" t="n">
+        <v>9.214554288594741</v>
+      </c>
+      <c r="O632" t="n">
+        <v>-8.69228551911845</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -34065,6 +37861,12 @@
       <c r="M633" t="n">
         <v>0</v>
       </c>
+      <c r="N633" t="n">
+        <v>9.550561868660974</v>
+      </c>
+      <c r="O633" t="n">
+        <v>-8.995719306522293</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -34108,6 +37910,12 @@
       <c r="M634" t="n">
         <v>0</v>
       </c>
+      <c r="N634" t="n">
+        <v>10.06276854559124</v>
+      </c>
+      <c r="O634" t="n">
+        <v>-9.45827081171109</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -34151,6 +37959,12 @@
       <c r="M635" t="n">
         <v>0</v>
       </c>
+      <c r="N635" t="n">
+        <v>11.9273873402646</v>
+      </c>
+      <c r="O635" t="n">
+        <v>-11.2136399850401</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -34194,6 +38008,12 @@
       <c r="M636" t="n">
         <v>0</v>
       </c>
+      <c r="N636" t="n">
+        <v>12.47600749501727</v>
+      </c>
+      <c r="O636" t="n">
+        <v>-11.73578826728906</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -34237,6 +38057,12 @@
       <c r="M637" t="n">
         <v>0</v>
       </c>
+      <c r="N637" t="n">
+        <v>15.43728046985664</v>
+      </c>
+      <c r="O637" t="n">
+        <v>-14.55417469310262</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -34280,6 +38106,12 @@
       <c r="M638" t="n">
         <v>0</v>
       </c>
+      <c r="N638" t="n">
+        <v>16.17049590299799</v>
+      </c>
+      <c r="O638" t="n">
+        <v>-15.25201121189728</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -34323,6 +38155,12 @@
       <c r="M639" t="n">
         <v>0</v>
       </c>
+      <c r="N639" t="n">
+        <v>3.135533917722148</v>
+      </c>
+      <c r="O639" t="n">
+        <v>-3.017800472933332</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -34366,6 +38204,12 @@
       <c r="M640" t="n">
         <v>0</v>
       </c>
+      <c r="N640" t="n">
+        <v>3.818355059775413</v>
+      </c>
+      <c r="O640" t="n">
+        <v>-3.642537585192254</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -34409,6 +38253,12 @@
       <c r="M641" t="n">
         <v>0</v>
       </c>
+      <c r="N641" t="n">
+        <v>3.590748012424324</v>
+      </c>
+      <c r="O641" t="n">
+        <v>-3.434291881105947</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -34452,6 +38302,12 @@
       <c r="M642" t="n">
         <v>0</v>
       </c>
+      <c r="N642" t="n">
+        <v>4.959679907715557</v>
+      </c>
+      <c r="O642" t="n">
+        <v>-4.687226749291514</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -34495,6 +38351,12 @@
       <c r="M643" t="n">
         <v>0</v>
       </c>
+      <c r="N643" t="n">
+        <v>5.189121032598216</v>
+      </c>
+      <c r="O643" t="n">
+        <v>-4.897401887721085</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -34538,6 +38400,12 @@
       <c r="M644" t="n">
         <v>0</v>
       </c>
+      <c r="N644" t="n">
+        <v>5.64800328236351</v>
+      </c>
+      <c r="O644" t="n">
+        <v>-5.317752164580225</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -34581,6 +38449,12 @@
       <c r="M645" t="n">
         <v>0</v>
       </c>
+      <c r="N645" t="n">
+        <v>10.22462667503175</v>
+      </c>
+      <c r="O645" t="n">
+        <v>-9.60443782743307</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -34624,6 +38498,12 @@
       <c r="M646" t="n">
         <v>0</v>
       </c>
+      <c r="N646" t="n">
+        <v>10.91137134191074</v>
+      </c>
+      <c r="O646" t="n">
+        <v>-10.24664851802572</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -34667,6 +38547,12 @@
       <c r="M647" t="n">
         <v>0</v>
       </c>
+      <c r="N647" t="n">
+        <v>13.42343829334485</v>
+      </c>
+      <c r="O647" t="n">
+        <v>-12.63750388894637</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -34710,6 +38596,12 @@
       <c r="M648" t="n">
         <v>0</v>
       </c>
+      <c r="N648" t="n">
+        <v>13.65180801620254</v>
+      </c>
+      <c r="O648" t="n">
+        <v>-12.8548543772119</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -34753,6 +38645,12 @@
       <c r="M649" t="n">
         <v>0</v>
       </c>
+      <c r="N649" t="n">
+        <v>4.546697587757203</v>
+      </c>
+      <c r="O649" t="n">
+        <v>-4.308923813502773</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -34796,6 +38694,12 @@
       <c r="M650" t="n">
         <v>0</v>
       </c>
+      <c r="N650" t="n">
+        <v>6.919948085421223</v>
+      </c>
+      <c r="O650" t="n">
+        <v>-6.50921094380848</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -34839,6 +38743,12 @@
       <c r="M651" t="n">
         <v>0</v>
       </c>
+      <c r="N651" t="n">
+        <v>10.28265238404613</v>
+      </c>
+      <c r="O651" t="n">
+        <v>-9.656838313902883</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -34882,6 +38792,12 @@
       <c r="M652" t="n">
         <v>0</v>
       </c>
+      <c r="N652" t="n">
+        <v>22.1699986786468</v>
+      </c>
+      <c r="O652" t="n">
+        <v>-20.96202758942623</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -34925,6 +38841,12 @@
       <c r="M653" t="n">
         <v>0</v>
       </c>
+      <c r="N653" t="n">
+        <v>2.679649833545354</v>
+      </c>
+      <c r="O653" t="n">
+        <v>-2.600696066721548</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -34968,6 +38890,12 @@
       <c r="M654" t="n">
         <v>0</v>
       </c>
+      <c r="N654" t="n">
+        <v>3.828974330002107</v>
+      </c>
+      <c r="O654" t="n">
+        <v>-3.652253527142034</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -35011,6 +38939,12 @@
       <c r="M655" t="n">
         <v>0</v>
       </c>
+      <c r="N655" t="n">
+        <v>6.02559701132502</v>
+      </c>
+      <c r="O655" t="n">
+        <v>-5.666854280477</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -35054,6 +38988,12 @@
       <c r="M656" t="n">
         <v>0</v>
       </c>
+      <c r="N656" t="n">
+        <v>9.232554694150149</v>
+      </c>
+      <c r="O656" t="n">
+        <v>-8.708540900090602</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -35097,6 +39037,12 @@
       <c r="M657" t="n">
         <v>0</v>
       </c>
+      <c r="N657" t="n">
+        <v>11.1234202829682</v>
+      </c>
+      <c r="O657" t="n">
+        <v>-10.44846573050314</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -35140,6 +39086,12 @@
       <c r="M658" t="n">
         <v>0</v>
       </c>
+      <c r="N658" t="n">
+        <v>13.9847129204887</v>
+      </c>
+      <c r="O658" t="n">
+        <v>-13.17169604341354</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -35183,6 +39135,12 @@
       <c r="M659" t="n">
         <v>0</v>
       </c>
+      <c r="N659" t="n">
+        <v>18.38882084536543</v>
+      </c>
+      <c r="O659" t="n">
+        <v>-17.36329813439936</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -35226,6 +39184,12 @@
       <c r="M660" t="n">
         <v>0</v>
       </c>
+      <c r="N660" t="n">
+        <v>25.75073894680367</v>
+      </c>
+      <c r="O660" t="n">
+        <v>-24.34827300179076</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -35269,6 +39233,12 @@
       <c r="M661" t="n">
         <v>0</v>
       </c>
+      <c r="N661" t="n">
+        <v>6.426922903315161</v>
+      </c>
+      <c r="O661" t="n">
+        <v>-6.043584079174755</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -35312,6 +39282,12 @@
       <c r="M662" t="n">
         <v>0</v>
       </c>
+      <c r="N662" t="n">
+        <v>20.02332328373403</v>
+      </c>
+      <c r="O662" t="n">
+        <v>-18.9189329996993</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -35355,6 +39331,12 @@
       <c r="M663" t="n">
         <v>0</v>
       </c>
+      <c r="N663" t="n">
+        <v>18.24203944545966</v>
+      </c>
+      <c r="O663" t="n">
+        <v>-17.22359919123765</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -35398,6 +39380,12 @@
       <c r="M664" t="n">
         <v>0</v>
       </c>
+      <c r="N664" t="n">
+        <v>17.62544119374935</v>
+      </c>
+      <c r="O664" t="n">
+        <v>-16.63675287292401</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -35441,6 +39429,12 @@
       <c r="M665" t="n">
         <v>0</v>
       </c>
+      <c r="N665" t="n">
+        <v>18.89401454663313</v>
+      </c>
+      <c r="O665" t="n">
+        <v>-17.82104368929349</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -35484,6 +39478,12 @@
       <c r="M666" t="n">
         <v>0</v>
       </c>
+      <c r="N666" t="n">
+        <v>4.890847570250759</v>
+      </c>
+      <c r="O666" t="n">
+        <v>-4.624174207762642</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -35527,6 +39527,12 @@
       <c r="M667" t="n">
         <v>0</v>
       </c>
+      <c r="N667" t="n">
+        <v>7.653338293113086</v>
+      </c>
+      <c r="O667" t="n">
+        <v>-7.177787787191404</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -35570,6 +39576,12 @@
       <c r="M668" t="n">
         <v>0.3451736190507124</v>
       </c>
+      <c r="N668" t="n">
+        <v>10.3294768872869</v>
+      </c>
+      <c r="O668" t="n">
+        <v>-9.68350836985215</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -35613,6 +39625,12 @@
       <c r="M669" t="n">
         <v>0</v>
       </c>
+      <c r="N669" t="n">
+        <v>13.07015157717125</v>
+      </c>
+      <c r="O669" t="n">
+        <v>-12.2701054872801</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -35656,6 +39674,12 @@
       <c r="M670" t="n">
         <v>0.8886749742435556</v>
       </c>
+      <c r="N670" t="n">
+        <v>8.390185763102687</v>
+      </c>
+      <c r="O670" t="n">
+        <v>-7.882151304062868</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -35699,6 +39723,12 @@
       <c r="M671" t="n">
         <v>1.044357263248827</v>
       </c>
+      <c r="N671" t="n">
+        <v>9.181144787797674</v>
+      </c>
+      <c r="O671" t="n">
+        <v>-8.635292858299822</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -35742,6 +39772,12 @@
       <c r="M672" t="n">
         <v>0.9140517839534916</v>
       </c>
+      <c r="N672" t="n">
+        <v>9.738213402117177</v>
+      </c>
+      <c r="O672" t="n">
+        <v>-9.159181731208196</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -35785,6 +39821,12 @@
       <c r="M673" t="n">
         <v>0.4961633513797672</v>
       </c>
+      <c r="N673" t="n">
+        <v>10.17254571841887</v>
+      </c>
+      <c r="O673" t="n">
+        <v>-9.544343354026033</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -35828,6 +39870,12 @@
       <c r="M674" t="n">
         <v>0</v>
       </c>
+      <c r="N674" t="n">
+        <v>11.71816205506628</v>
+      </c>
+      <c r="O674" t="n">
+        <v>-10.98219947337343</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -35871,6 +39919,12 @@
       <c r="M675" t="n">
         <v>0</v>
       </c>
+      <c r="N675" t="n">
+        <v>12.2556444351292</v>
+      </c>
+      <c r="O675" t="n">
+        <v>-11.4939127446571</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -35914,6 +39968,12 @@
       <c r="M676" t="n">
         <v>0</v>
       </c>
+      <c r="N676" t="n">
+        <v>15.14941377207385</v>
+      </c>
+      <c r="O676" t="n">
+        <v>-14.25192683338803</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -35957,6 +40017,12 @@
       <c r="M677" t="n">
         <v>0</v>
       </c>
+      <c r="N677" t="n">
+        <v>15.86582719336449</v>
+      </c>
+      <c r="O677" t="n">
+        <v>-14.93476684001765</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -36000,6 +40066,12 @@
       <c r="M678" t="n">
         <v>0</v>
       </c>
+      <c r="N678" t="n">
+        <v>3.135533906065505</v>
+      </c>
+      <c r="O678" t="n">
+        <v>-3.017800460670642</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -36043,6 +40115,12 @@
       <c r="M679" t="n">
         <v>0</v>
       </c>
+      <c r="N679" t="n">
+        <v>3.81835504236793</v>
+      </c>
+      <c r="O679" t="n">
+        <v>-3.642537566879733</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -36086,6 +40164,12 @@
       <c r="M680" t="n">
         <v>0</v>
       </c>
+      <c r="N680" t="n">
+        <v>3.590747996933803</v>
+      </c>
+      <c r="O680" t="n">
+        <v>-3.434291864810039</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -36129,6 +40213,12 @@
       <c r="M681" t="n">
         <v>0</v>
       </c>
+      <c r="N681" t="n">
+        <v>4.959679870481026</v>
+      </c>
+      <c r="O681" t="n">
+        <v>-4.687226710121115</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -36172,6 +40262,12 @@
       <c r="M682" t="n">
         <v>0</v>
       </c>
+      <c r="N682" t="n">
+        <v>5.189120992730717</v>
+      </c>
+      <c r="O682" t="n">
+        <v>-4.89740184578083</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -36215,6 +40311,12 @@
       <c r="M683" t="n">
         <v>0</v>
       </c>
+      <c r="N683" t="n">
+        <v>5.648003237230091</v>
+      </c>
+      <c r="O683" t="n">
+        <v>-5.317752117100255</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -36258,6 +40360,12 @@
       <c r="M684" t="n">
         <v>0.3641099380649901</v>
       </c>
+      <c r="N684" t="n">
+        <v>10.30979542530194</v>
+      </c>
+      <c r="O684" t="n">
+        <v>-9.666055043095096</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -36301,6 +40409,12 @@
       <c r="M685" t="n">
         <v>0.0008966753971133319</v>
       </c>
+      <c r="N685" t="n">
+        <v>10.64692192096454</v>
+      </c>
+      <c r="O685" t="n">
+        <v>-9.958840839390115</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -36344,6 +40458,12 @@
       <c r="M686" t="n">
         <v>0</v>
       </c>
+      <c r="N686" t="n">
+        <v>13.18171983329117</v>
+      </c>
+      <c r="O686" t="n">
+        <v>-12.3764452995792</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -36387,6 +40507,12 @@
       <c r="M687" t="n">
         <v>0</v>
       </c>
+      <c r="N687" t="n">
+        <v>13.40485634553106</v>
+      </c>
+      <c r="O687" t="n">
+        <v>-12.5891249241774</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -36430,6 +40556,12 @@
       <c r="M688" t="n">
         <v>0</v>
       </c>
+      <c r="N688" t="n">
+        <v>4.546697599528052</v>
+      </c>
+      <c r="O688" t="n">
+        <v>-4.30892382588561</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -36473,6 +40605,12 @@
       <c r="M689" t="n">
         <v>0</v>
       </c>
+      <c r="N689" t="n">
+        <v>6.743355142740043</v>
+      </c>
+      <c r="O689" t="n">
+        <v>-6.323436633550207</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -36516,6 +40654,12 @@
       <c r="M690" t="n">
         <v>0.3167691405293414</v>
       </c>
+      <c r="N690" t="n">
+        <v>10.35899908026448</v>
+      </c>
+      <c r="O690" t="n">
+        <v>-9.709688359987831</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -36559,6 +40703,12 @@
       <c r="M691" t="n">
         <v>0</v>
       </c>
+      <c r="N691" t="n">
+        <v>21.72784825208003</v>
+      </c>
+      <c r="O691" t="n">
+        <v>-20.52207492169079</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -36602,6 +40752,12 @@
       <c r="M692" t="n">
         <v>0</v>
       </c>
+      <c r="N692" t="n">
+        <v>2.679650149181641</v>
+      </c>
+      <c r="O692" t="n">
+        <v>-2.600696501492975</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -36645,6 +40801,12 @@
       <c r="M693" t="n">
         <v>0</v>
       </c>
+      <c r="N693" t="n">
+        <v>3.828974332501667</v>
+      </c>
+      <c r="O693" t="n">
+        <v>-3.65225352977155</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -36688,6 +40850,12 @@
       <c r="M694" t="n">
         <v>0</v>
       </c>
+      <c r="N694" t="n">
+        <v>6.001953191642637</v>
+      </c>
+      <c r="O694" t="n">
+        <v>-5.641981178377452</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -36731,6 +40899,12 @@
       <c r="M695" t="n">
         <v>1.017892423795962</v>
       </c>
+      <c r="N695" t="n">
+        <v>9.236882452881288</v>
+      </c>
+      <c r="O695" t="n">
+        <v>-8.689143382496439</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -36774,6 +40948,12 @@
       <c r="M696" t="n">
         <v>0</v>
       </c>
+      <c r="N696" t="n">
+        <v>10.86918197374929</v>
+      </c>
+      <c r="O696" t="n">
+        <v>-10.1711053719338</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -36817,6 +40997,12 @@
       <c r="M697" t="n">
         <v>0</v>
       </c>
+      <c r="N697" t="n">
+        <v>13.73013256140769</v>
+      </c>
+      <c r="O697" t="n">
+        <v>-12.89915766059028</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -36860,6 +41046,12 @@
       <c r="M698" t="n">
         <v>0</v>
       </c>
+      <c r="N698" t="n">
+        <v>18.03331806951241</v>
+      </c>
+      <c r="O698" t="n">
+        <v>-17.000682190364</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -36903,6 +41095,12 @@
       <c r="M699" t="n">
         <v>0</v>
       </c>
+      <c r="N699" t="n">
+        <v>24.92821163954995</v>
+      </c>
+      <c r="O699" t="n">
+        <v>-23.53777590777847</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -36946,6 +41144,12 @@
       <c r="M700" t="n">
         <v>0</v>
       </c>
+      <c r="N700" t="n">
+        <v>6.336326657011461</v>
+      </c>
+      <c r="O700" t="n">
+        <v>-5.948277579868935</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -36989,6 +41193,12 @@
       <c r="M701" t="n">
         <v>0</v>
       </c>
+      <c r="N701" t="n">
+        <v>19.63036503702486</v>
+      </c>
+      <c r="O701" t="n">
+        <v>-18.52288645046761</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -37032,6 +41242,12 @@
       <c r="M702" t="n">
         <v>0</v>
       </c>
+      <c r="N702" t="n">
+        <v>17.88990024155345</v>
+      </c>
+      <c r="O702" t="n">
+        <v>-16.86398537860153</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -37075,6 +41291,12 @@
       <c r="M703" t="n">
         <v>0</v>
       </c>
+      <c r="N703" t="n">
+        <v>17.28743165850566</v>
+      </c>
+      <c r="O703" t="n">
+        <v>-16.28975039218634</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -37118,6 +41340,12 @@
       <c r="M704" t="n">
         <v>0</v>
       </c>
+      <c r="N704" t="n">
+        <v>15.79299839951587</v>
+      </c>
+      <c r="O704" t="n">
+        <v>-14.5679752672819</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -37161,6 +41389,12 @@
       <c r="M705" t="n">
         <v>0</v>
       </c>
+      <c r="N705" t="n">
+        <v>5.05550222078051</v>
+      </c>
+      <c r="O705" t="n">
+        <v>-4.797376585577942</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -37204,6 +41438,12 @@
       <c r="M706" t="n">
         <v>0</v>
       </c>
+      <c r="N706" t="n">
+        <v>7.845869113077183</v>
+      </c>
+      <c r="O706" t="n">
+        <v>-7.380305258350843</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -37247,6 +41487,12 @@
       <c r="M707" t="n">
         <v>0</v>
       </c>
+      <c r="N707" t="n">
+        <v>10.82925090649987</v>
+      </c>
+      <c r="O707" t="n">
+        <v>-10.1447194152994</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -37290,6 +41536,12 @@
       <c r="M708" t="n">
         <v>0</v>
       </c>
+      <c r="N708" t="n">
+        <v>12.58175665926926</v>
+      </c>
+      <c r="O708" t="n">
+        <v>-11.70570678052186</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -37333,6 +41585,12 @@
       <c r="M709" t="n">
         <v>0</v>
       </c>
+      <c r="N709" t="n">
+        <v>8.413457878854018</v>
+      </c>
+      <c r="O709" t="n">
+        <v>-7.906607951966988</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -37376,6 +41634,12 @@
       <c r="M710" t="n">
         <v>0</v>
       </c>
+      <c r="N710" t="n">
+        <v>9.172469180786326</v>
+      </c>
+      <c r="O710" t="n">
+        <v>-8.61065333644623</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -37419,6 +41683,12 @@
       <c r="M711" t="n">
         <v>0</v>
       </c>
+      <c r="N711" t="n">
+        <v>10.08914244108673</v>
+      </c>
+      <c r="O711" t="n">
+        <v>-9.485227696177043</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -37462,6 +41732,12 @@
       <c r="M712" t="n">
         <v>0</v>
       </c>
+      <c r="N712" t="n">
+        <v>10.63381459197447</v>
+      </c>
+      <c r="O712" t="n">
+        <v>-9.970640889623981</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -37505,6 +41781,12 @@
       <c r="M713" t="n">
         <v>0</v>
       </c>
+      <c r="N713" t="n">
+        <v>11.84018888261485</v>
+      </c>
+      <c r="O713" t="n">
+        <v>-11.04517945957907</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -37548,6 +41830,12 @@
       <c r="M714" t="n">
         <v>0</v>
       </c>
+      <c r="N714" t="n">
+        <v>12.134601655926</v>
+      </c>
+      <c r="O714" t="n">
+        <v>-11.30741803915153</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -37591,6 +41879,12 @@
       <c r="M715" t="n">
         <v>0</v>
       </c>
+      <c r="N715" t="n">
+        <v>13.72374595093761</v>
+      </c>
+      <c r="O715" t="n">
+        <v>-12.72289651168064</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -37634,6 +41928,12 @@
       <c r="M716" t="n">
         <v>0</v>
       </c>
+      <c r="N716" t="n">
+        <v>14.11777328184313</v>
+      </c>
+      <c r="O716" t="n">
+        <v>-13.07394941958439</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -37677,6 +41977,12 @@
       <c r="M717" t="n">
         <v>0</v>
       </c>
+      <c r="N717" t="n">
+        <v>3.199545878948973</v>
+      </c>
+      <c r="O717" t="n">
+        <v>-3.085134785825331</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -37720,6 +42026,12 @@
       <c r="M718" t="n">
         <v>0</v>
       </c>
+      <c r="N718" t="n">
+        <v>3.92255314708519</v>
+      </c>
+      <c r="O718" t="n">
+        <v>-3.75214456028061</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -37763,6 +42075,12 @@
       <c r="M719" t="n">
         <v>0</v>
       </c>
+      <c r="N719" t="n">
+        <v>3.681526449039892</v>
+      </c>
+      <c r="O719" t="n">
+        <v>-3.529782431283101</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -37806,6 +42124,12 @@
       <c r="M720" t="n">
         <v>0</v>
       </c>
+      <c r="N720" t="n">
+        <v>5.127818110227275</v>
+      </c>
+      <c r="O720" t="n">
+        <v>-4.864093514027259</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -37849,6 +42173,12 @@
       <c r="M721" t="n">
         <v>0</v>
       </c>
+      <c r="N721" t="n">
+        <v>5.36893744041308</v>
+      </c>
+      <c r="O721" t="n">
+        <v>-5.086553091509491</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -37892,6 +42222,12 @@
       <c r="M722" t="n">
         <v>0</v>
       </c>
+      <c r="N722" t="n">
+        <v>5.856625906807558</v>
+      </c>
+      <c r="O722" t="n">
+        <v>-5.53720541139915</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -37935,6 +42271,12 @@
       <c r="M723" t="n">
         <v>0</v>
       </c>
+      <c r="N723" t="n">
+        <v>10.80466979990711</v>
+      </c>
+      <c r="O723" t="n">
+        <v>-10.12281965303428</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -37978,6 +42320,12 @@
       <c r="M724" t="n">
         <v>0</v>
       </c>
+      <c r="N724" t="n">
+        <v>11.29488124960412</v>
+      </c>
+      <c r="O724" t="n">
+        <v>-10.55945952382222</v>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -38021,6 +42369,12 @@
       <c r="M725" t="n">
         <v>0</v>
       </c>
+      <c r="N725" t="n">
+        <v>12.64296273627121</v>
+      </c>
+      <c r="O725" t="n">
+        <v>-11.76021916848928</v>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -38064,6 +42418,12 @@
       <c r="M726" t="n">
         <v>0</v>
       </c>
+      <c r="N726" t="n">
+        <v>12.7655155986955</v>
+      </c>
+      <c r="O726" t="n">
+        <v>-11.86937913618629</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -38107,6 +42467,12 @@
       <c r="M727" t="n">
         <v>0</v>
       </c>
+      <c r="N727" t="n">
+        <v>4.693924758721081</v>
+      </c>
+      <c r="O727" t="n">
+        <v>-4.463794031723537</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -38150,6 +42516,12 @@
       <c r="M728" t="n">
         <v>0</v>
       </c>
+      <c r="N728" t="n">
+        <v>7.024186821789121</v>
+      </c>
+      <c r="O728" t="n">
+        <v>-6.618848896779027</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -38193,6 +42565,12 @@
       <c r="M729" t="n">
         <v>0</v>
       </c>
+      <c r="N729" t="n">
+        <v>10.8659462311192</v>
+      </c>
+      <c r="O729" t="n">
+        <v>-10.17739963688277</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -38236,6 +42614,12 @@
       <c r="M730" t="n">
         <v>0</v>
       </c>
+      <c r="N730" t="n">
+        <v>17.36063591371854</v>
+      </c>
+      <c r="O730" t="n">
+        <v>-15.96604592847577</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -38279,6 +42663,12 @@
       <c r="M731" t="n">
         <v>0</v>
       </c>
+      <c r="N731" t="n">
+        <v>2.716946692136815</v>
+      </c>
+      <c r="O731" t="n">
+        <v>-2.63992828922206</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -38322,6 +42712,12 @@
       <c r="M732" t="n">
         <v>0</v>
       </c>
+      <c r="N732" t="n">
+        <v>3.933801767593744</v>
+      </c>
+      <c r="O732" t="n">
+        <v>-3.762522529830467</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -38365,6 +42761,12 @@
       <c r="M733" t="n">
         <v>0</v>
       </c>
+      <c r="N733" t="n">
+        <v>6.239852239700741</v>
+      </c>
+      <c r="O733" t="n">
+        <v>-5.892231565305242</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -38408,6 +42810,12 @@
       <c r="M734" t="n">
         <v>0</v>
       </c>
+      <c r="N734" t="n">
+        <v>9.212392130354567</v>
+      </c>
+      <c r="O734" t="n">
+        <v>-8.647813238331819</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -38451,6 +42859,12 @@
       <c r="M735" t="n">
         <v>0</v>
       </c>
+      <c r="N735" t="n">
+        <v>11.408675689539</v>
+      </c>
+      <c r="O735" t="n">
+        <v>-10.6608182121602</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -38494,6 +42908,12 @@
       <c r="M736" t="n">
         <v>0</v>
       </c>
+      <c r="N736" t="n">
+        <v>12.9441664655307</v>
+      </c>
+      <c r="O736" t="n">
+        <v>-12.02850657284507</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -38537,6 +42957,12 @@
       <c r="M737" t="n">
         <v>0</v>
       </c>
+      <c r="N737" t="n">
+        <v>15.31678272283094</v>
+      </c>
+      <c r="O737" t="n">
+        <v>-14.14326432892464</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -38580,6 +43006,12 @@
       <c r="M738" t="n">
         <v>0</v>
       </c>
+      <c r="N738" t="n">
+        <v>19.54555010446859</v>
+      </c>
+      <c r="O738" t="n">
+        <v>-17.91463078831486</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -38623,6 +43055,12 @@
       <c r="M739" t="n">
         <v>0</v>
       </c>
+      <c r="N739" t="n">
+        <v>6.601879004062982</v>
+      </c>
+      <c r="O739" t="n">
+        <v>-6.227617671503147</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -38666,6 +43104,12 @@
       <c r="M740" t="n">
         <v>0</v>
       </c>
+      <c r="N740" t="n">
+        <v>16.20028600450594</v>
+      </c>
+      <c r="O740" t="n">
+        <v>-14.93120425149852</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -38709,6 +43153,12 @@
       <c r="M741" t="n">
         <v>0</v>
       </c>
+      <c r="N741" t="n">
+        <v>15.23744246281942</v>
+      </c>
+      <c r="O741" t="n">
+        <v>-14.072505838688</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -38751,6 +43201,12 @@
       </c>
       <c r="M742" t="n">
         <v>0</v>
+      </c>
+      <c r="N742" t="n">
+        <v>14.90415046762026</v>
+      </c>
+      <c r="O742" t="n">
+        <v>-13.77526408040746</v>
       </c>
     </row>
   </sheetData>
